--- a/inst/extdata/Verbatims_fake_survey.xlsx
+++ b/inst/extdata/Verbatims_fake_survey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Codestufen" sheetId="1" state="visible" r:id="rId2"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="114">
   <si>
     <t xml:space="preserve">love </t>
   </si>
@@ -425,6 +425,12 @@
     <t xml:space="preserve">Calc3 Zuord 10</t>
   </si>
   <si>
+    <t xml:space="preserve">q6_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THIS id value is not in the data!!!</t>
+  </si>
+  <si>
     <t xml:space="preserve">q6mcg</t>
   </si>
 </sst>
@@ -667,7 +673,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -795,6 +801,10 @@
     <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -19009,7 +19019,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BD132"/>
+  <dimension ref="A1:BD134"/>
   <sheetFormatPr defaultColWidth="11.43359375" defaultRowHeight="11.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="1" style="7" width="11.52"/>
@@ -28389,8 +28399,32 @@
       <c r="BC132" s="29"/>
       <c r="BD132" s="29"/>
     </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D133" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E133" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D134" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E134" s="7" t="n">
+        <v>9999999</v>
+      </c>
+      <c r="F134" s="32" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="false" formatColumns="false" formatRows="false" sort="false" autoFilter="false"/>
   <autoFilter ref="D32:BD132"/>
   <mergeCells count="2">
     <mergeCell ref="H11:J14"/>
@@ -28447,7 +28481,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E1" s="9"/>
       <c r="F1" s="10"/>

--- a/inst/extdata/Verbatims_fake_survey.xlsx
+++ b/inst/extdata/Verbatims_fake_survey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Codestufen" sheetId="1" state="visible" r:id="rId2"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="115">
   <si>
     <t xml:space="preserve">love </t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t xml:space="preserve">noch wat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;reserved&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Others</t>
@@ -1237,7 +1240,9 @@
         <f aca="false">A5+1</f>
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
@@ -2158,16 +2163,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2186,16 +2191,16 @@
         <v>99</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7646,7 +7651,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" s="9"/>
       <c r="F1" s="10"/>
@@ -7691,16 +7696,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="16"/>
       <c r="J3" s="17"/>
@@ -7732,7 +7737,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="17"/>
     </row>
@@ -7740,16 +7745,16 @@
       <c r="A5" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B5" s="7" t="n">
+      <c r="B5" s="7" t="str">
         <f aca="false">Codestufen!B6</f>
-        <v>0</v>
+        <v>&lt;reserved&gt;</v>
       </c>
       <c r="C5" s="7" t="n">
         <f aca="false">COUNTIF(V_W_Q6_Zuord,A5)</f>
         <v>0</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="19" t="n">
         <f aca="false">(4-D3)*20+1</f>
@@ -7767,7 +7772,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" s="17"/>
     </row>
@@ -7803,7 +7808,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -7820,7 +7825,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="19" t="n">
         <f aca="false">E6+1</f>
@@ -7839,7 +7844,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="17"/>
     </row>
@@ -7876,7 +7881,7 @@
         <v>100</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -7893,7 +7898,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">E8+1</f>
@@ -7901,7 +7906,7 @@
       </c>
       <c r="F9" s="20" t="str">
         <f aca="false">HYPERLINK("#Codestufen!"&amp;ADDRESS(E9+1,D$6),IF(INDEX(V_W_Q6_CodestufenName,E9)=0,"",INDEX(V_W_Q6_CodestufenName,E9)))</f>
-        <v/>
+        <v>&lt;reserved&gt;</v>
       </c>
       <c r="G9" s="19" t="n">
         <f aca="false">INDEX(V_W_Q6_Codestufen,E9)</f>
@@ -7940,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -7958,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">E10+1</f>
@@ -8024,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">E12+1</f>
@@ -8087,7 +8092,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" s="19" t="n">
         <f aca="false">E14+1</f>
@@ -8147,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="19" t="n">
         <f aca="false">E16+1</f>
@@ -8213,7 +8218,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="19" t="n">
         <f aca="false">E18+1</f>
@@ -8244,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" s="19" t="n">
         <f aca="false">E19+1</f>
@@ -8275,7 +8280,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="19" t="n">
         <f aca="false">E20+1</f>
@@ -8306,7 +8311,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">E21+1</f>
@@ -8337,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">E22+1</f>
@@ -8425,7 +8430,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">D29</f>
@@ -8456,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" s="19" t="n">
         <f aca="false">E26+1</f>
@@ -8487,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" s="19" t="n">
         <f aca="false">E27+1</f>
@@ -8588,55 +8593,55 @@
         <v>0</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I32" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J32" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K32" s="28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L32" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M32" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N32" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O32" s="28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P32" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q32" s="28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R32" s="28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S32" s="28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T32" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8652,13 +8657,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E33" s="29" t="n">
         <v>7</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G33" s="31" t="n">
         <v>1</v>
@@ -8702,13 +8707,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E34" s="29" t="n">
         <v>17</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G34" s="31" t="n">
         <v>1</v>
@@ -8752,13 +8757,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E35" s="29" t="n">
         <v>23</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G35" s="31" t="n">
         <v>1</v>
@@ -8802,13 +8807,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E36" s="29" t="n">
         <v>51</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G36" s="31" t="n">
         <v>1</v>
@@ -8852,13 +8857,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E37" s="29" t="n">
         <v>58</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G37" s="31" t="n">
         <v>1</v>
@@ -8902,13 +8907,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E38" s="29" t="n">
         <v>65</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G38" s="31" t="n">
         <v>1</v>
@@ -8952,13 +8957,13 @@
         <v>0</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E39" s="29" t="n">
         <v>67</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G39" s="31" t="n">
         <v>1</v>
@@ -9002,13 +9007,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E40" s="29" t="n">
         <v>73</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G40" s="31" t="n">
         <v>1</v>
@@ -9052,13 +9057,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E41" s="29" t="n">
         <v>74</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G41" s="31" t="n">
         <v>1</v>
@@ -9102,13 +9107,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E42" s="29" t="n">
         <v>91</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G42" s="31" t="n">
         <v>1</v>
@@ -9152,13 +9157,13 @@
         <v>0</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E43" s="29" t="n">
         <v>100</v>
       </c>
       <c r="F43" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G43" s="31" t="n">
         <v>1</v>
@@ -9202,13 +9207,13 @@
         <v>0</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E44" s="29" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G44" s="31" t="n">
         <v>2</v>
@@ -9252,13 +9257,13 @@
         <v>0</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E45" s="29" t="n">
         <v>13</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G45" s="31" t="n">
         <v>2</v>
@@ -9302,13 +9307,13 @@
         <v>0</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E46" s="29" t="n">
         <v>22</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G46" s="31" t="n">
         <v>2</v>
@@ -9352,13 +9357,13 @@
         <v>0</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E47" s="29" t="n">
         <v>26</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G47" s="31" t="n">
         <v>2</v>
@@ -9402,13 +9407,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E48" s="29" t="n">
         <v>35</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G48" s="31" t="n">
         <v>2</v>
@@ -9452,13 +9457,13 @@
         <v>0</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E49" s="29" t="n">
         <v>38</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G49" s="31" t="n">
         <v>2</v>
@@ -9502,13 +9507,13 @@
         <v>0</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E50" s="29" t="n">
         <v>45</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" s="31" t="n">
         <v>2</v>
@@ -9552,13 +9557,13 @@
         <v>0</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E51" s="29" t="n">
         <v>47</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G51" s="31" t="n">
         <v>2</v>
@@ -9602,13 +9607,13 @@
         <v>0</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E52" s="29" t="n">
         <v>55</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G52" s="31" t="n">
         <v>2</v>
@@ -9652,13 +9657,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E53" s="29" t="n">
         <v>72</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G53" s="31" t="n">
         <v>2</v>
@@ -9702,13 +9707,13 @@
         <v>0</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E54" s="29" t="n">
         <v>78</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G54" s="31" t="n">
         <v>2</v>
@@ -9752,13 +9757,13 @@
         <v>0</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E55" s="29" t="n">
         <v>88</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G55" s="31" t="n">
         <v>2</v>
@@ -9802,13 +9807,13 @@
         <v>0</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E56" s="29" t="n">
         <v>89</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G56" s="31" t="n">
         <v>2</v>
@@ -9852,13 +9857,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E57" s="29" t="n">
         <v>97</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G57" s="31" t="n">
         <v>2</v>
@@ -9902,13 +9907,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E58" s="29" t="n">
         <v>5</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G58" s="31" t="n">
         <v>3</v>
@@ -9952,13 +9957,13 @@
         <v>0</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E59" s="29" t="n">
         <v>12</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G59" s="31" t="n">
         <v>3</v>
@@ -10002,13 +10007,13 @@
         <v>0</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E60" s="29" t="n">
         <v>14</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G60" s="31" t="n">
         <v>3</v>
@@ -10052,13 +10057,13 @@
         <v>0</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E61" s="29" t="n">
         <v>39</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G61" s="31" t="n">
         <v>3</v>
@@ -10102,13 +10107,13 @@
         <v>0</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E62" s="29" t="n">
         <v>49</v>
       </c>
       <c r="F62" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G62" s="31" t="n">
         <v>3</v>
@@ -10152,13 +10157,13 @@
         <v>0</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E63" s="29" t="n">
         <v>62</v>
       </c>
       <c r="F63" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G63" s="31" t="n">
         <v>3</v>
@@ -10202,13 +10207,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E64" s="29" t="n">
         <v>79</v>
       </c>
       <c r="F64" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G64" s="31" t="n">
         <v>3</v>
@@ -10252,13 +10257,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E65" s="29" t="n">
         <v>98</v>
       </c>
       <c r="F65" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G65" s="31" t="n">
         <v>3</v>
@@ -10302,13 +10307,13 @@
         <v>0</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E66" s="29" t="n">
         <v>8</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G66" s="31" t="n">
         <v>1</v>
@@ -10352,13 +10357,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E67" s="29" t="n">
         <v>9</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G67" s="31" t="n">
         <v>1</v>
@@ -10402,13 +10407,13 @@
         <v>0</v>
       </c>
       <c r="D68" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E68" s="29" t="n">
         <v>24</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G68" s="31" t="n">
         <v>1</v>
@@ -10452,13 +10457,13 @@
         <v>0</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E69" s="29" t="n">
         <v>30</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G69" s="31" t="n">
         <v>1</v>
@@ -10502,13 +10507,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E70" s="29" t="n">
         <v>32</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G70" s="31" t="n">
         <v>1</v>
@@ -10552,13 +10557,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E71" s="29" t="n">
         <v>36</v>
       </c>
       <c r="F71" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G71" s="31" t="n">
         <v>1</v>
@@ -10602,13 +10607,13 @@
         <v>0</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E72" s="29" t="n">
         <v>53</v>
       </c>
       <c r="F72" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G72" s="31" t="n">
         <v>1</v>
@@ -10652,13 +10657,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E73" s="29" t="n">
         <v>61</v>
       </c>
       <c r="F73" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G73" s="31" t="n">
         <v>1</v>
@@ -10702,13 +10707,13 @@
         <v>0</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E74" s="29" t="n">
         <v>70</v>
       </c>
       <c r="F74" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G74" s="31" t="n">
         <v>1</v>
@@ -10752,13 +10757,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E75" s="29" t="n">
         <v>4</v>
       </c>
       <c r="F75" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G75" s="31" t="n">
         <v>2</v>
@@ -10802,13 +10807,13 @@
         <v>0</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E76" s="29" t="n">
         <v>6</v>
       </c>
       <c r="F76" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G76" s="31" t="n">
         <v>2</v>
@@ -10852,13 +10857,13 @@
         <v>0</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E77" s="29" t="n">
         <v>19</v>
       </c>
       <c r="F77" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G77" s="31" t="n">
         <v>2</v>
@@ -10902,13 +10907,13 @@
         <v>0</v>
       </c>
       <c r="D78" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E78" s="29" t="n">
         <v>25</v>
       </c>
       <c r="F78" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G78" s="31" t="n">
         <v>2</v>
@@ -10952,13 +10957,13 @@
         <v>0</v>
       </c>
       <c r="D79" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E79" s="29" t="n">
         <v>28</v>
       </c>
       <c r="F79" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G79" s="31" t="n">
         <v>2</v>
@@ -11002,13 +11007,13 @@
         <v>0</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E80" s="29" t="n">
         <v>34</v>
       </c>
       <c r="F80" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G80" s="31" t="n">
         <v>2</v>
@@ -11052,13 +11057,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E81" s="29" t="n">
         <v>44</v>
       </c>
       <c r="F81" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G81" s="31" t="n">
         <v>2</v>
@@ -11102,13 +11107,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E82" s="29" t="n">
         <v>52</v>
       </c>
       <c r="F82" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G82" s="31" t="n">
         <v>2</v>
@@ -11152,13 +11157,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E83" s="29" t="n">
         <v>54</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G83" s="31" t="n">
         <v>2</v>
@@ -11202,13 +11207,13 @@
         <v>0</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E84" s="29" t="n">
         <v>56</v>
       </c>
       <c r="F84" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G84" s="31" t="n">
         <v>2</v>
@@ -11252,13 +11257,13 @@
         <v>0</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E85" s="29" t="n">
         <v>57</v>
       </c>
       <c r="F85" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G85" s="31" t="n">
         <v>2</v>
@@ -11302,13 +11307,13 @@
         <v>0</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E86" s="29" t="n">
         <v>66</v>
       </c>
       <c r="F86" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G86" s="31" t="n">
         <v>2</v>
@@ -11352,13 +11357,13 @@
         <v>0</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E87" s="29" t="n">
         <v>71</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G87" s="31" t="n">
         <v>2</v>
@@ -11402,13 +11407,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E88" s="29" t="n">
         <v>77</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G88" s="31" t="n">
         <v>2</v>
@@ -11452,13 +11457,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E89" s="29" t="n">
         <v>83</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G89" s="31" t="n">
         <v>2</v>
@@ -11502,13 +11507,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E90" s="29" t="n">
         <v>85</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G90" s="31" t="n">
         <v>2</v>
@@ -11552,13 +11557,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E91" s="29" t="n">
         <v>90</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G91" s="31" t="n">
         <v>2</v>
@@ -11602,13 +11607,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E92" s="29" t="n">
         <v>94</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G92" s="31" t="n">
         <v>2</v>
@@ -11652,13 +11657,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E93" s="29" t="n">
         <v>96</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G93" s="31" t="n">
         <v>2</v>
@@ -11702,13 +11707,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E94" s="29" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G94" s="31" t="n">
         <v>3</v>
@@ -11752,13 +11757,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E95" s="29" t="n">
         <v>15</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G95" s="31" t="n">
         <v>3</v>
@@ -11802,13 +11807,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E96" s="29" t="n">
         <v>21</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G96" s="31" t="n">
         <v>3</v>
@@ -11852,13 +11857,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E97" s="29" t="n">
         <v>27</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G97" s="31" t="n">
         <v>3</v>
@@ -11902,13 +11907,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E98" s="29" t="n">
         <v>37</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G98" s="31" t="n">
         <v>3</v>
@@ -11952,13 +11957,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E99" s="29" t="n">
         <v>40</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G99" s="31" t="n">
         <v>3</v>
@@ -12002,13 +12007,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E100" s="29" t="n">
         <v>63</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G100" s="31" t="n">
         <v>3</v>
@@ -12041,13 +12046,13 @@
     </row>
     <row r="101" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D101" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E101" s="29" t="n">
         <v>69</v>
       </c>
       <c r="F101" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G101" s="31" t="n">
         <v>3</v>
@@ -12080,13 +12085,13 @@
     </row>
     <row r="102" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D102" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E102" s="29" t="n">
         <v>76</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G102" s="31" t="n">
         <v>3</v>
@@ -12119,13 +12124,13 @@
     </row>
     <row r="103" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D103" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E103" s="29" t="n">
         <v>99</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G103" s="31" t="n">
         <v>3</v>
@@ -12158,13 +12163,13 @@
     </row>
     <row r="104" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E104" s="29" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G104" s="31" t="n">
         <v>1</v>
@@ -12197,13 +12202,13 @@
     </row>
     <row r="105" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E105" s="29" t="n">
         <v>10</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G105" s="31" t="n">
         <v>1</v>
@@ -12236,13 +12241,13 @@
     </row>
     <row r="106" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D106" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E106" s="29" t="n">
         <v>16</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G106" s="31" t="n">
         <v>1</v>
@@ -12275,13 +12280,13 @@
     </row>
     <row r="107" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E107" s="29" t="n">
         <v>33</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G107" s="31" t="n">
         <v>1</v>
@@ -12314,13 +12319,13 @@
     </row>
     <row r="108" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D108" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E108" s="29" t="n">
         <v>41</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G108" s="31" t="n">
         <v>1</v>
@@ -12353,13 +12358,13 @@
     </row>
     <row r="109" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D109" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E109" s="29" t="n">
         <v>42</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G109" s="31" t="n">
         <v>1</v>
@@ -12392,13 +12397,13 @@
     </row>
     <row r="110" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D110" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E110" s="29" t="n">
         <v>68</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G110" s="31" t="n">
         <v>1</v>
@@ -12431,13 +12436,13 @@
     </row>
     <row r="111" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D111" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E111" s="29" t="n">
         <v>75</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G111" s="31" t="n">
         <v>1</v>
@@ -12470,13 +12475,13 @@
     </row>
     <row r="112" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E112" s="29" t="n">
         <v>82</v>
       </c>
       <c r="F112" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G112" s="31" t="n">
         <v>1</v>
@@ -12509,13 +12514,13 @@
     </row>
     <row r="113" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D113" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E113" s="29" t="n">
         <v>86</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G113" s="31" t="n">
         <v>1</v>
@@ -12548,13 +12553,13 @@
     </row>
     <row r="114" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D114" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E114" s="29" t="n">
         <v>93</v>
       </c>
       <c r="F114" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G114" s="31" t="n">
         <v>1</v>
@@ -12587,13 +12592,13 @@
     </row>
     <row r="115" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D115" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E115" s="29" t="n">
         <v>11</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G115" s="31" t="n">
         <v>2</v>
@@ -12626,13 +12631,13 @@
     </row>
     <row r="116" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E116" s="29" t="n">
         <v>20</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G116" s="31" t="n">
         <v>2</v>
@@ -12665,13 +12670,13 @@
     </row>
     <row r="117" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D117" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E117" s="29" t="n">
         <v>29</v>
       </c>
       <c r="F117" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G117" s="31" t="n">
         <v>2</v>
@@ -12704,13 +12709,13 @@
     </row>
     <row r="118" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D118" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E118" s="29" t="n">
         <v>46</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G118" s="31" t="n">
         <v>2</v>
@@ -12743,13 +12748,13 @@
     </row>
     <row r="119" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D119" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E119" s="29" t="n">
         <v>50</v>
       </c>
       <c r="F119" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G119" s="31" t="n">
         <v>2</v>
@@ -12782,13 +12787,13 @@
     </row>
     <row r="120" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E120" s="29" t="n">
         <v>81</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G120" s="31" t="n">
         <v>2</v>
@@ -12821,13 +12826,13 @@
     </row>
     <row r="121" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D121" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E121" s="29" t="n">
         <v>84</v>
       </c>
       <c r="F121" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G121" s="31" t="n">
         <v>2</v>
@@ -12860,13 +12865,13 @@
     </row>
     <row r="122" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D122" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E122" s="29" t="n">
         <v>87</v>
       </c>
       <c r="F122" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G122" s="31" t="n">
         <v>2</v>
@@ -12899,13 +12904,13 @@
     </row>
     <row r="123" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D123" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E123" s="29" t="n">
         <v>18</v>
       </c>
       <c r="F123" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G123" s="31" t="n">
         <v>3</v>
@@ -12938,13 +12943,13 @@
     </row>
     <row r="124" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D124" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E124" s="29" t="n">
         <v>31</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G124" s="31" t="n">
         <v>3</v>
@@ -12977,13 +12982,13 @@
     </row>
     <row r="125" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D125" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E125" s="29" t="n">
         <v>43</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G125" s="31" t="n">
         <v>3</v>
@@ -13016,13 +13021,13 @@
     </row>
     <row r="126" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D126" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E126" s="29" t="n">
         <v>48</v>
       </c>
       <c r="F126" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G126" s="31" t="n">
         <v>3</v>
@@ -13055,13 +13060,13 @@
     </row>
     <row r="127" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E127" s="29" t="n">
         <v>59</v>
       </c>
       <c r="F127" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G127" s="31" t="n">
         <v>3</v>
@@ -13094,13 +13099,13 @@
     </row>
     <row r="128" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E128" s="29" t="n">
         <v>60</v>
       </c>
       <c r="F128" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G128" s="31" t="n">
         <v>3</v>
@@ -13133,13 +13138,13 @@
     </row>
     <row r="129" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D129" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E129" s="29" t="n">
         <v>64</v>
       </c>
       <c r="F129" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G129" s="31" t="n">
         <v>3</v>
@@ -13172,13 +13177,13 @@
     </row>
     <row r="130" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E130" s="29" t="n">
         <v>80</v>
       </c>
       <c r="F130" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G130" s="31" t="n">
         <v>3</v>
@@ -13211,13 +13216,13 @@
     </row>
     <row r="131" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E131" s="29" t="n">
         <v>92</v>
       </c>
       <c r="F131" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G131" s="31" t="n">
         <v>3</v>
@@ -13250,13 +13255,13 @@
     </row>
     <row r="132" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D132" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E132" s="29" t="n">
         <v>95</v>
       </c>
       <c r="F132" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G132" s="31" t="n">
         <v>3</v>
@@ -13345,7 +13350,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E1" s="9"/>
       <c r="F1" s="10"/>
@@ -13390,16 +13395,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="16"/>
       <c r="J3" s="17"/>
@@ -13431,7 +13436,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="17"/>
     </row>
@@ -13448,7 +13453,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="19" t="n">
         <f aca="false">(4-D3)*20+1</f>
@@ -13466,7 +13471,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" s="17"/>
     </row>
@@ -13502,7 +13507,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -13519,7 +13524,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="19" t="n">
         <f aca="false">E6+1</f>
@@ -13538,7 +13543,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="17"/>
     </row>
@@ -13575,7 +13580,7 @@
         <v>100</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -13592,7 +13597,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">E8+1</f>
@@ -13639,7 +13644,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -13657,7 +13662,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">E10+1</f>
@@ -13723,7 +13728,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">E12+1</f>
@@ -13786,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" s="19" t="n">
         <f aca="false">E14+1</f>
@@ -13846,7 +13851,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="19" t="n">
         <f aca="false">E16+1</f>
@@ -13912,7 +13917,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="19" t="n">
         <f aca="false">E18+1</f>
@@ -13943,7 +13948,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" s="19" t="n">
         <f aca="false">E19+1</f>
@@ -13974,7 +13979,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="19" t="n">
         <f aca="false">E20+1</f>
@@ -14005,7 +14010,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">E21+1</f>
@@ -14036,7 +14041,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">E22+1</f>
@@ -14124,7 +14129,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">D29</f>
@@ -14155,7 +14160,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" s="19" t="n">
         <f aca="false">E26+1</f>
@@ -14186,7 +14191,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" s="19" t="n">
         <f aca="false">E27+1</f>
@@ -14287,55 +14292,55 @@
         <v>0</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I32" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J32" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K32" s="28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L32" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M32" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N32" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O32" s="28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P32" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q32" s="28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R32" s="28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S32" s="28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T32" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14351,13 +14356,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33" s="29" t="n">
         <v>77</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G33" s="31" t="n">
         <v>1</v>
@@ -14401,13 +14406,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E34" s="29" t="n">
         <v>87</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G34" s="31" t="n">
         <v>1</v>
@@ -14451,13 +14456,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E35" s="29" t="n">
         <v>6</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G35" s="31" t="n">
         <v>4</v>
@@ -14501,13 +14506,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E36" s="29" t="n">
         <v>15</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G36" s="31" t="n">
         <v>4</v>
@@ -14551,13 +14556,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E37" s="29" t="n">
         <v>23</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G37" s="31" t="n">
         <v>4</v>
@@ -14601,13 +14606,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E38" s="29" t="n">
         <v>27</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G38" s="31" t="n">
         <v>4</v>
@@ -14651,13 +14656,13 @@
         <v>0</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E39" s="29" t="n">
         <v>44</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G39" s="31" t="n">
         <v>4</v>
@@ -14701,13 +14706,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E40" s="29" t="n">
         <v>45</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G40" s="31" t="n">
         <v>4</v>
@@ -14751,13 +14756,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E41" s="29" t="n">
         <v>49</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G41" s="31" t="n">
         <v>4</v>
@@ -14801,13 +14806,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42" s="29" t="n">
         <v>56</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G42" s="31" t="n">
         <v>4</v>
@@ -14851,13 +14856,13 @@
         <v>0</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E43" s="29" t="n">
         <v>66</v>
       </c>
       <c r="F43" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G43" s="31" t="n">
         <v>4</v>
@@ -14901,13 +14906,13 @@
         <v>0</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E44" s="29" t="n">
         <v>69</v>
       </c>
       <c r="F44" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G44" s="31" t="n">
         <v>4</v>
@@ -14951,13 +14956,13 @@
         <v>0</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E45" s="29" t="n">
         <v>98</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G45" s="31" t="n">
         <v>4</v>
@@ -15001,13 +15006,13 @@
         <v>0</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E46" s="29" t="n">
         <v>5</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G46" s="31" t="n">
         <v>2</v>
@@ -15051,13 +15056,13 @@
         <v>0</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E47" s="29" t="n">
         <v>11</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G47" s="31" t="n">
         <v>2</v>
@@ -15101,13 +15106,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E48" s="29" t="n">
         <v>19</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G48" s="31" t="n">
         <v>2</v>
@@ -15151,13 +15156,13 @@
         <v>0</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E49" s="29" t="n">
         <v>29</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G49" s="31" t="n">
         <v>2</v>
@@ -15201,13 +15206,13 @@
         <v>0</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E50" s="29" t="n">
         <v>41</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G50" s="31" t="n">
         <v>2</v>
@@ -15251,13 +15256,13 @@
         <v>0</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E51" s="29" t="n">
         <v>46</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G51" s="31" t="n">
         <v>2</v>
@@ -15301,13 +15306,13 @@
         <v>0</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E52" s="29" t="n">
         <v>51</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G52" s="31" t="n">
         <v>2</v>
@@ -15351,13 +15356,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E53" s="29" t="n">
         <v>57</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G53" s="31" t="n">
         <v>2</v>
@@ -15401,13 +15406,13 @@
         <v>0</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E54" s="29" t="n">
         <v>61</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G54" s="31" t="n">
         <v>2</v>
@@ -15451,13 +15456,13 @@
         <v>0</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E55" s="29" t="n">
         <v>63</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G55" s="31" t="n">
         <v>2</v>
@@ -15501,13 +15506,13 @@
         <v>0</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E56" s="29" t="n">
         <v>73</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G56" s="31" t="n">
         <v>2</v>
@@ -15551,13 +15556,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E57" s="29" t="n">
         <v>75</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G57" s="31" t="n">
         <v>2</v>
@@ -15601,13 +15606,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E58" s="29" t="n">
         <v>84</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G58" s="31" t="n">
         <v>2</v>
@@ -15651,13 +15656,13 @@
         <v>0</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E59" s="29" t="n">
         <v>92</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G59" s="31" t="n">
         <v>2</v>
@@ -15701,13 +15706,13 @@
         <v>0</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E60" s="29" t="n">
         <v>7</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G60" s="31" t="n">
         <v>1</v>
@@ -15751,13 +15756,13 @@
         <v>0</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E61" s="29" t="n">
         <v>9</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G61" s="31" t="n">
         <v>1</v>
@@ -15801,13 +15806,13 @@
         <v>0</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E62" s="29" t="n">
         <v>13</v>
       </c>
       <c r="F62" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G62" s="31" t="n">
         <v>1</v>
@@ -15851,13 +15856,13 @@
         <v>0</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E63" s="29" t="n">
         <v>16</v>
       </c>
       <c r="F63" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G63" s="31" t="n">
         <v>1</v>
@@ -15901,13 +15906,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E64" s="29" t="n">
         <v>32</v>
       </c>
       <c r="F64" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G64" s="31" t="n">
         <v>1</v>
@@ -15951,13 +15956,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E65" s="29" t="n">
         <v>48</v>
       </c>
       <c r="F65" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G65" s="31" t="n">
         <v>1</v>
@@ -16001,13 +16006,13 @@
         <v>0</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E66" s="29" t="n">
         <v>59</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G66" s="31" t="n">
         <v>1</v>
@@ -16051,13 +16056,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E67" s="29" t="n">
         <v>79</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G67" s="31" t="n">
         <v>1</v>
@@ -16101,13 +16106,13 @@
         <v>0</v>
       </c>
       <c r="D68" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E68" s="29" t="n">
         <v>82</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G68" s="31" t="n">
         <v>1</v>
@@ -16151,13 +16156,13 @@
         <v>0</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E69" s="29" t="n">
         <v>91</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G69" s="31" t="n">
         <v>1</v>
@@ -16201,13 +16206,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E70" s="29" t="n">
         <v>99</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G70" s="31" t="n">
         <v>1</v>
@@ -16251,13 +16256,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E71" s="29" t="n">
         <v>17</v>
       </c>
       <c r="F71" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G71" s="31" t="n">
         <v>4</v>
@@ -16301,13 +16306,13 @@
         <v>0</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E72" s="29" t="n">
         <v>25</v>
       </c>
       <c r="F72" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G72" s="31" t="n">
         <v>4</v>
@@ -16351,13 +16356,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E73" s="29" t="n">
         <v>31</v>
       </c>
       <c r="F73" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G73" s="31" t="n">
         <v>4</v>
@@ -16401,13 +16406,13 @@
         <v>0</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E74" s="29" t="n">
         <v>54</v>
       </c>
       <c r="F74" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G74" s="31" t="n">
         <v>4</v>
@@ -16451,13 +16456,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E75" s="29" t="n">
         <v>71</v>
       </c>
       <c r="F75" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G75" s="31" t="n">
         <v>4</v>
@@ -16501,13 +16506,13 @@
         <v>0</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E76" s="29" t="n">
         <v>81</v>
       </c>
       <c r="F76" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G76" s="31" t="n">
         <v>4</v>
@@ -16551,13 +16556,13 @@
         <v>0</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E77" s="29" t="n">
         <v>94</v>
       </c>
       <c r="F77" s="30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G77" s="31" t="n">
         <v>4</v>
@@ -16601,13 +16606,13 @@
         <v>0</v>
       </c>
       <c r="D78" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E78" s="29" t="n">
         <v>18</v>
       </c>
       <c r="F78" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G78" s="31" t="n">
         <v>2</v>
@@ -16651,13 +16656,13 @@
         <v>0</v>
       </c>
       <c r="D79" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E79" s="29" t="n">
         <v>21</v>
       </c>
       <c r="F79" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G79" s="31" t="n">
         <v>2</v>
@@ -16701,13 +16706,13 @@
         <v>0</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E80" s="29" t="n">
         <v>33</v>
       </c>
       <c r="F80" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G80" s="31" t="n">
         <v>2</v>
@@ -16751,13 +16756,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E81" s="29" t="n">
         <v>67</v>
       </c>
       <c r="F81" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G81" s="31" t="n">
         <v>2</v>
@@ -16801,13 +16806,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E82" s="29" t="n">
         <v>68</v>
       </c>
       <c r="F82" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G82" s="31" t="n">
         <v>2</v>
@@ -16851,13 +16856,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E83" s="29" t="n">
         <v>90</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G83" s="31" t="n">
         <v>2</v>
@@ -16901,13 +16906,13 @@
         <v>0</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E84" s="29" t="n">
         <v>96</v>
       </c>
       <c r="F84" s="30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G84" s="31" t="n">
         <v>2</v>
@@ -16951,13 +16956,13 @@
         <v>0</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E85" s="29" t="n">
         <v>2</v>
       </c>
       <c r="F85" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G85" s="31" t="n">
         <v>1</v>
@@ -17001,13 +17006,13 @@
         <v>0</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E86" s="29" t="n">
         <v>3</v>
       </c>
       <c r="F86" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G86" s="31" t="n">
         <v>1</v>
@@ -17051,13 +17056,13 @@
         <v>0</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E87" s="29" t="n">
         <v>34</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G87" s="31" t="n">
         <v>1</v>
@@ -17101,13 +17106,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E88" s="29" t="n">
         <v>42</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G88" s="31" t="n">
         <v>1</v>
@@ -17151,13 +17156,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E89" s="29" t="n">
         <v>47</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G89" s="31" t="n">
         <v>1</v>
@@ -17201,13 +17206,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E90" s="29" t="n">
         <v>62</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G90" s="31" t="n">
         <v>1</v>
@@ -17251,13 +17256,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E91" s="29" t="n">
         <v>24</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G91" s="31" t="n">
         <v>4</v>
@@ -17301,13 +17306,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E92" s="29" t="n">
         <v>35</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G92" s="31" t="n">
         <v>4</v>
@@ -17351,13 +17356,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E93" s="29" t="n">
         <v>52</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G93" s="31" t="n">
         <v>4</v>
@@ -17401,13 +17406,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E94" s="29" t="n">
         <v>58</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G94" s="31" t="n">
         <v>4</v>
@@ -17451,13 +17456,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E95" s="29" t="n">
         <v>70</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G95" s="31" t="n">
         <v>4</v>
@@ -17501,13 +17506,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E96" s="29" t="n">
         <v>76</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G96" s="31" t="n">
         <v>4</v>
@@ -17551,13 +17556,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E97" s="29" t="n">
         <v>80</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G97" s="31" t="n">
         <v>4</v>
@@ -17601,13 +17606,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E98" s="29" t="n">
         <v>14</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G98" s="31" t="n">
         <v>2</v>
@@ -17651,13 +17656,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E99" s="29" t="n">
         <v>20</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G99" s="31" t="n">
         <v>2</v>
@@ -17701,13 +17706,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E100" s="29" t="n">
         <v>26</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G100" s="31" t="n">
         <v>2</v>
@@ -17740,13 +17745,13 @@
     </row>
     <row r="101" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D101" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E101" s="29" t="n">
         <v>50</v>
       </c>
       <c r="F101" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G101" s="31" t="n">
         <v>2</v>
@@ -17779,13 +17784,13 @@
     </row>
     <row r="102" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D102" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E102" s="29" t="n">
         <v>78</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G102" s="31" t="n">
         <v>2</v>
@@ -17818,13 +17823,13 @@
     </row>
     <row r="103" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D103" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E103" s="29" t="n">
         <v>88</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G103" s="31" t="n">
         <v>2</v>
@@ -17857,13 +17862,13 @@
     </row>
     <row r="104" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E104" s="29" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G104" s="31" t="n">
         <v>3</v>
@@ -17896,13 +17901,13 @@
     </row>
     <row r="105" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E105" s="29" t="n">
         <v>28</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G105" s="31" t="n">
         <v>3</v>
@@ -17935,13 +17940,13 @@
     </row>
     <row r="106" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D106" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E106" s="29" t="n">
         <v>30</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G106" s="31" t="n">
         <v>3</v>
@@ -17974,13 +17979,13 @@
     </row>
     <row r="107" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E107" s="29" t="n">
         <v>36</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G107" s="31" t="n">
         <v>3</v>
@@ -18013,13 +18018,13 @@
     </row>
     <row r="108" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D108" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E108" s="29" t="n">
         <v>40</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G108" s="31" t="n">
         <v>3</v>
@@ -18052,13 +18057,13 @@
     </row>
     <row r="109" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D109" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E109" s="29" t="n">
         <v>60</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G109" s="31" t="n">
         <v>3</v>
@@ -18091,13 +18096,13 @@
     </row>
     <row r="110" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D110" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E110" s="29" t="n">
         <v>72</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G110" s="31" t="n">
         <v>3</v>
@@ -18130,13 +18135,13 @@
     </row>
     <row r="111" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D111" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E111" s="29" t="n">
         <v>83</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G111" s="31" t="n">
         <v>3</v>
@@ -18169,13 +18174,13 @@
     </row>
     <row r="112" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E112" s="29" t="n">
         <v>85</v>
       </c>
       <c r="F112" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G112" s="31" t="n">
         <v>3</v>
@@ -18208,13 +18213,13 @@
     </row>
     <row r="113" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D113" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E113" s="29" t="n">
         <v>95</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G113" s="31" t="n">
         <v>3</v>
@@ -18247,13 +18252,13 @@
     </row>
     <row r="114" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D114" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E114" s="29" t="n">
         <v>97</v>
       </c>
       <c r="F114" s="30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G114" s="31" t="n">
         <v>3</v>
@@ -18286,13 +18291,13 @@
     </row>
     <row r="115" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D115" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E115" s="29" t="n">
         <v>4</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G115" s="31" t="n">
         <v>3</v>
@@ -18325,13 +18330,13 @@
     </row>
     <row r="116" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E116" s="29" t="n">
         <v>8</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G116" s="31" t="n">
         <v>3</v>
@@ -18364,13 +18369,13 @@
     </row>
     <row r="117" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D117" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E117" s="29" t="n">
         <v>10</v>
       </c>
       <c r="F117" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G117" s="31" t="n">
         <v>3</v>
@@ -18403,13 +18408,13 @@
     </row>
     <row r="118" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D118" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E118" s="29" t="n">
         <v>12</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G118" s="31" t="n">
         <v>3</v>
@@ -18442,13 +18447,13 @@
     </row>
     <row r="119" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D119" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E119" s="29" t="n">
         <v>22</v>
       </c>
       <c r="F119" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G119" s="31" t="n">
         <v>3</v>
@@ -18481,13 +18486,13 @@
     </row>
     <row r="120" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E120" s="29" t="n">
         <v>38</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G120" s="31" t="n">
         <v>3</v>
@@ -18520,13 +18525,13 @@
     </row>
     <row r="121" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D121" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E121" s="29" t="n">
         <v>55</v>
       </c>
       <c r="F121" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G121" s="31" t="n">
         <v>3</v>
@@ -18559,13 +18564,13 @@
     </row>
     <row r="122" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D122" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E122" s="29" t="n">
         <v>65</v>
       </c>
       <c r="F122" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G122" s="31" t="n">
         <v>3</v>
@@ -18598,13 +18603,13 @@
     </row>
     <row r="123" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D123" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E123" s="29" t="n">
         <v>74</v>
       </c>
       <c r="F123" s="30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G123" s="31" t="n">
         <v>3</v>
@@ -18637,13 +18642,13 @@
     </row>
     <row r="124" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D124" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E124" s="29" t="n">
         <v>37</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G124" s="31" t="n">
         <v>3</v>
@@ -18676,13 +18681,13 @@
     </row>
     <row r="125" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D125" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E125" s="29" t="n">
         <v>39</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G125" s="31" t="n">
         <v>3</v>
@@ -18715,13 +18720,13 @@
     </row>
     <row r="126" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D126" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E126" s="29" t="n">
         <v>43</v>
       </c>
       <c r="F126" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G126" s="31" t="n">
         <v>3</v>
@@ -18754,13 +18759,13 @@
     </row>
     <row r="127" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E127" s="29" t="n">
         <v>53</v>
       </c>
       <c r="F127" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G127" s="31" t="n">
         <v>3</v>
@@ -18793,13 +18798,13 @@
     </row>
     <row r="128" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E128" s="29" t="n">
         <v>64</v>
       </c>
       <c r="F128" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G128" s="31" t="n">
         <v>3</v>
@@ -18832,13 +18837,13 @@
     </row>
     <row r="129" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D129" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E129" s="29" t="n">
         <v>86</v>
       </c>
       <c r="F129" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G129" s="31" t="n">
         <v>3</v>
@@ -18871,13 +18876,13 @@
     </row>
     <row r="130" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E130" s="29" t="n">
         <v>89</v>
       </c>
       <c r="F130" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G130" s="31" t="n">
         <v>3</v>
@@ -18910,13 +18915,13 @@
     </row>
     <row r="131" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E131" s="29" t="n">
         <v>93</v>
       </c>
       <c r="F131" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G131" s="31" t="n">
         <v>3</v>
@@ -18949,13 +18954,13 @@
     </row>
     <row r="132" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D132" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E132" s="29" t="n">
         <v>100</v>
       </c>
       <c r="F132" s="30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G132" s="31" t="n">
         <v>3</v>
@@ -19044,7 +19049,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1" s="9"/>
       <c r="F1" s="10"/>
@@ -19089,16 +19094,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="16"/>
       <c r="J3" s="17"/>
@@ -19130,7 +19135,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="17"/>
     </row>
@@ -19147,7 +19152,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="19" t="n">
         <f aca="false">(4-D3)*20+1</f>
@@ -19165,7 +19170,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" s="17"/>
     </row>
@@ -19201,7 +19206,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -19218,7 +19223,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="19" t="n">
         <f aca="false">E6+1</f>
@@ -19237,7 +19242,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="17"/>
     </row>
@@ -19274,7 +19279,7 @@
         <v>103</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -19291,7 +19296,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">E8+1</f>
@@ -19338,7 +19343,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -19356,7 +19361,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">E10+1</f>
@@ -19422,7 +19427,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">E12+1</f>
@@ -19485,7 +19490,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" s="19" t="n">
         <f aca="false">E14+1</f>
@@ -19545,7 +19550,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="19" t="n">
         <f aca="false">E16+1</f>
@@ -19611,7 +19616,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="19" t="n">
         <f aca="false">E18+1</f>
@@ -19642,7 +19647,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" s="19" t="n">
         <f aca="false">E19+1</f>
@@ -19673,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="19" t="n">
         <f aca="false">E20+1</f>
@@ -19704,7 +19709,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">E21+1</f>
@@ -19735,7 +19740,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">E22+1</f>
@@ -19823,7 +19828,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">D29</f>
@@ -19854,7 +19859,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" s="19" t="n">
         <f aca="false">E26+1</f>
@@ -19885,7 +19890,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" s="19" t="n">
         <f aca="false">E27+1</f>
@@ -19986,163 +19991,163 @@
         <v>0</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I32" s="28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J32" s="28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K32" s="28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L32" s="28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M32" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N32" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O32" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P32" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q32" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R32" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S32" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T32" s="28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U32" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V32" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W32" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X32" s="28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y32" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z32" s="28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AA32" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AB32" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AC32" s="28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AD32" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AE32" s="28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AF32" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG32" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH32" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI32" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AJ32" s="28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AK32" s="28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AL32" s="28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AM32" s="28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AN32" s="28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AO32" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AP32" s="28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AQ32" s="28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AR32" s="28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AS32" s="28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AT32" s="28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU32" s="28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV32" s="28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AW32" s="28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AX32" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AY32" s="28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ32" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BA32" s="28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BB32" s="28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BC32" s="28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="BD32" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20158,13 +20163,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E33" s="29" t="n">
         <v>7</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G33" s="31" t="n">
         <v>1</v>
@@ -20246,13 +20251,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E34" s="29" t="n">
         <v>17</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G34" s="31" t="n">
         <v>1</v>
@@ -20332,13 +20337,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E35" s="29" t="n">
         <v>23</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G35" s="31" t="n">
         <v>1</v>
@@ -20418,13 +20423,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E36" s="29" t="n">
         <v>51</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G36" s="31" t="n">
         <v>1</v>
@@ -20504,13 +20509,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E37" s="29" t="n">
         <v>58</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G37" s="31" t="n">
         <v>1</v>
@@ -20592,13 +20597,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E38" s="29" t="n">
         <v>65</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G38" s="31" t="n">
         <v>1</v>
@@ -20678,13 +20683,13 @@
         <v>0</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E39" s="29" t="n">
         <v>67</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G39" s="31" t="n">
         <v>1</v>
@@ -20764,13 +20769,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E40" s="29" t="n">
         <v>73</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G40" s="31" t="n">
         <v>1</v>
@@ -20852,13 +20857,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E41" s="29" t="n">
         <v>74</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G41" s="31" t="n">
         <v>1</v>
@@ -20938,13 +20943,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E42" s="29" t="n">
         <v>91</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G42" s="31" t="n">
         <v>1</v>
@@ -21024,13 +21029,13 @@
         <v>0</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E43" s="29" t="n">
         <v>100</v>
       </c>
       <c r="F43" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G43" s="31" t="n">
         <v>1</v>
@@ -21110,13 +21115,13 @@
         <v>0</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E44" s="29" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G44" s="31" t="n">
         <v>2</v>
@@ -21196,13 +21201,13 @@
         <v>0</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E45" s="29" t="n">
         <v>13</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G45" s="31" t="n">
         <v>2</v>
@@ -21282,13 +21287,13 @@
         <v>0</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E46" s="29" t="n">
         <v>22</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G46" s="31" t="n">
         <v>2</v>
@@ -21368,13 +21373,13 @@
         <v>0</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E47" s="29" t="n">
         <v>26</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G47" s="31" t="n">
         <v>2</v>
@@ -21454,13 +21459,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E48" s="29" t="n">
         <v>35</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G48" s="31" t="n">
         <v>2</v>
@@ -21540,13 +21545,13 @@
         <v>0</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E49" s="29" t="n">
         <v>38</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G49" s="31" t="n">
         <v>2</v>
@@ -21626,13 +21631,13 @@
         <v>0</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E50" s="29" t="n">
         <v>45</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" s="31" t="n">
         <v>2</v>
@@ -21712,13 +21717,13 @@
         <v>0</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E51" s="29" t="n">
         <v>47</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G51" s="31" t="n">
         <v>2</v>
@@ -21798,13 +21803,13 @@
         <v>0</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E52" s="29" t="n">
         <v>55</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G52" s="31" t="n">
         <v>2</v>
@@ -21884,13 +21889,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E53" s="29" t="n">
         <v>72</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G53" s="31" t="n">
         <v>2</v>
@@ -21970,13 +21975,13 @@
         <v>0</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E54" s="29" t="n">
         <v>78</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G54" s="31" t="n">
         <v>2</v>
@@ -22056,13 +22061,13 @@
         <v>0</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E55" s="29" t="n">
         <v>88</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G55" s="31" t="n">
         <v>2</v>
@@ -22142,13 +22147,13 @@
         <v>0</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E56" s="29" t="n">
         <v>89</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G56" s="31" t="n">
         <v>2</v>
@@ -22228,13 +22233,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E57" s="29" t="n">
         <v>97</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G57" s="31" t="n">
         <v>2</v>
@@ -22314,13 +22319,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E58" s="29" t="n">
         <v>5</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G58" s="31" t="n">
         <v>3</v>
@@ -22400,13 +22405,13 @@
         <v>0</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E59" s="29" t="n">
         <v>12</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G59" s="31" t="n">
         <v>3</v>
@@ -22486,13 +22491,13 @@
         <v>0</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E60" s="29" t="n">
         <v>14</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G60" s="31" t="n">
         <v>3</v>
@@ -22572,13 +22577,13 @@
         <v>0</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E61" s="29" t="n">
         <v>39</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G61" s="31" t="n">
         <v>3</v>
@@ -22658,13 +22663,13 @@
         <v>0</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E62" s="29" t="n">
         <v>49</v>
       </c>
       <c r="F62" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G62" s="31" t="n">
         <v>3</v>
@@ -22744,13 +22749,13 @@
         <v>0</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E63" s="29" t="n">
         <v>62</v>
       </c>
       <c r="F63" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G63" s="31" t="n">
         <v>3</v>
@@ -22830,13 +22835,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E64" s="29" t="n">
         <v>79</v>
       </c>
       <c r="F64" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G64" s="31" t="n">
         <v>3</v>
@@ -22916,13 +22921,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E65" s="29" t="n">
         <v>98</v>
       </c>
       <c r="F65" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G65" s="31" t="n">
         <v>3</v>
@@ -23002,13 +23007,13 @@
         <v>0</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E66" s="29" t="n">
         <v>8</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G66" s="31" t="n">
         <v>1</v>
@@ -23088,13 +23093,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E67" s="29" t="n">
         <v>9</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G67" s="31" t="n">
         <v>1</v>
@@ -23174,13 +23179,13 @@
         <v>0</v>
       </c>
       <c r="D68" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E68" s="29" t="n">
         <v>24</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G68" s="31" t="n">
         <v>1</v>
@@ -23260,13 +23265,13 @@
         <v>0</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E69" s="29" t="n">
         <v>30</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G69" s="31" t="n">
         <v>1</v>
@@ -23346,13 +23351,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E70" s="29" t="n">
         <v>32</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G70" s="31" t="n">
         <v>1</v>
@@ -23432,13 +23437,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E71" s="29" t="n">
         <v>36</v>
       </c>
       <c r="F71" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G71" s="31" t="n">
         <v>1</v>
@@ -23518,13 +23523,13 @@
         <v>0</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E72" s="29" t="n">
         <v>53</v>
       </c>
       <c r="F72" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G72" s="31" t="n">
         <v>1</v>
@@ -23604,13 +23609,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E73" s="29" t="n">
         <v>61</v>
       </c>
       <c r="F73" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G73" s="31" t="n">
         <v>1</v>
@@ -23690,13 +23695,13 @@
         <v>0</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E74" s="29" t="n">
         <v>70</v>
       </c>
       <c r="F74" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G74" s="31" t="n">
         <v>1</v>
@@ -23776,13 +23781,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E75" s="29" t="n">
         <v>4</v>
       </c>
       <c r="F75" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G75" s="31" t="n">
         <v>2</v>
@@ -23862,13 +23867,13 @@
         <v>0</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E76" s="29" t="n">
         <v>6</v>
       </c>
       <c r="F76" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G76" s="31" t="n">
         <v>2</v>
@@ -23948,13 +23953,13 @@
         <v>0</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E77" s="29" t="n">
         <v>19</v>
       </c>
       <c r="F77" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G77" s="31" t="n">
         <v>2</v>
@@ -24034,13 +24039,13 @@
         <v>0</v>
       </c>
       <c r="D78" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E78" s="29" t="n">
         <v>25</v>
       </c>
       <c r="F78" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G78" s="31" t="n">
         <v>2</v>
@@ -24120,13 +24125,13 @@
         <v>0</v>
       </c>
       <c r="D79" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E79" s="29" t="n">
         <v>28</v>
       </c>
       <c r="F79" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G79" s="31" t="n">
         <v>2</v>
@@ -24206,13 +24211,13 @@
         <v>0</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E80" s="29" t="n">
         <v>34</v>
       </c>
       <c r="F80" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G80" s="31" t="n">
         <v>2</v>
@@ -24292,13 +24297,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E81" s="29" t="n">
         <v>44</v>
       </c>
       <c r="F81" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G81" s="31" t="n">
         <v>2</v>
@@ -24378,13 +24383,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E82" s="29" t="n">
         <v>52</v>
       </c>
       <c r="F82" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G82" s="31" t="n">
         <v>2</v>
@@ -24464,13 +24469,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E83" s="29" t="n">
         <v>54</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G83" s="31" t="n">
         <v>2</v>
@@ -24550,13 +24555,13 @@
         <v>0</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E84" s="29" t="n">
         <v>56</v>
       </c>
       <c r="F84" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G84" s="31" t="n">
         <v>2</v>
@@ -24636,13 +24641,13 @@
         <v>0</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E85" s="29" t="n">
         <v>57</v>
       </c>
       <c r="F85" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G85" s="31" t="n">
         <v>2</v>
@@ -24722,13 +24727,13 @@
         <v>0</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E86" s="29" t="n">
         <v>66</v>
       </c>
       <c r="F86" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G86" s="31" t="n">
         <v>2</v>
@@ -24808,13 +24813,13 @@
         <v>0</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E87" s="29" t="n">
         <v>71</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G87" s="31" t="n">
         <v>2</v>
@@ -24894,13 +24899,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E88" s="29" t="n">
         <v>77</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G88" s="31" t="n">
         <v>2</v>
@@ -24980,13 +24985,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E89" s="29" t="n">
         <v>83</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G89" s="31" t="n">
         <v>2</v>
@@ -25066,13 +25071,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E90" s="29" t="n">
         <v>85</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G90" s="31" t="n">
         <v>2</v>
@@ -25152,13 +25157,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E91" s="29" t="n">
         <v>90</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G91" s="31" t="n">
         <v>2</v>
@@ -25238,13 +25243,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E92" s="29" t="n">
         <v>94</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G92" s="31" t="n">
         <v>2</v>
@@ -25324,13 +25329,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E93" s="29" t="n">
         <v>96</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G93" s="31" t="n">
         <v>2</v>
@@ -25410,13 +25415,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E94" s="29" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G94" s="31" t="n">
         <v>3</v>
@@ -25496,13 +25501,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E95" s="29" t="n">
         <v>15</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G95" s="31" t="n">
         <v>3</v>
@@ -25582,13 +25587,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E96" s="29" t="n">
         <v>21</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G96" s="31" t="n">
         <v>3</v>
@@ -25668,13 +25673,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E97" s="29" t="n">
         <v>27</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G97" s="31" t="n">
         <v>3</v>
@@ -25754,13 +25759,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E98" s="29" t="n">
         <v>37</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G98" s="31" t="n">
         <v>3</v>
@@ -25840,13 +25845,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E99" s="29" t="n">
         <v>40</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G99" s="31" t="n">
         <v>3</v>
@@ -25926,13 +25931,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E100" s="29" t="n">
         <v>63</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G100" s="31" t="n">
         <v>3</v>
@@ -26001,13 +26006,13 @@
     </row>
     <row r="101" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D101" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E101" s="29" t="n">
         <v>69</v>
       </c>
       <c r="F101" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G101" s="31" t="n">
         <v>3</v>
@@ -26076,13 +26081,13 @@
     </row>
     <row r="102" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D102" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E102" s="29" t="n">
         <v>76</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G102" s="31" t="n">
         <v>3</v>
@@ -26151,13 +26156,13 @@
     </row>
     <row r="103" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D103" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E103" s="29" t="n">
         <v>99</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G103" s="31" t="n">
         <v>3</v>
@@ -26226,13 +26231,13 @@
     </row>
     <row r="104" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E104" s="29" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G104" s="31" t="n">
         <v>1</v>
@@ -26301,13 +26306,13 @@
     </row>
     <row r="105" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E105" s="29" t="n">
         <v>10</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G105" s="31" t="n">
         <v>1</v>
@@ -26376,13 +26381,13 @@
     </row>
     <row r="106" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D106" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E106" s="29" t="n">
         <v>16</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G106" s="31" t="n">
         <v>1</v>
@@ -26451,13 +26456,13 @@
     </row>
     <row r="107" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E107" s="29" t="n">
         <v>33</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G107" s="31" t="n">
         <v>1</v>
@@ -26526,13 +26531,13 @@
     </row>
     <row r="108" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D108" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E108" s="29" t="n">
         <v>41</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G108" s="31" t="n">
         <v>1</v>
@@ -26601,13 +26606,13 @@
     </row>
     <row r="109" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D109" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E109" s="29" t="n">
         <v>42</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G109" s="31" t="n">
         <v>1</v>
@@ -26676,13 +26681,13 @@
     </row>
     <row r="110" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D110" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E110" s="29" t="n">
         <v>68</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G110" s="31" t="n">
         <v>1</v>
@@ -26751,13 +26756,13 @@
     </row>
     <row r="111" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D111" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E111" s="29" t="n">
         <v>75</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G111" s="31" t="n">
         <v>1</v>
@@ -26826,13 +26831,13 @@
     </row>
     <row r="112" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E112" s="29" t="n">
         <v>82</v>
       </c>
       <c r="F112" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G112" s="31" t="n">
         <v>1</v>
@@ -26901,13 +26906,13 @@
     </row>
     <row r="113" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D113" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E113" s="29" t="n">
         <v>86</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G113" s="31" t="n">
         <v>1</v>
@@ -26976,13 +26981,13 @@
     </row>
     <row r="114" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D114" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E114" s="29" t="n">
         <v>93</v>
       </c>
       <c r="F114" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G114" s="31" t="n">
         <v>1</v>
@@ -27051,13 +27056,13 @@
     </row>
     <row r="115" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D115" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E115" s="29" t="n">
         <v>11</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G115" s="31" t="n">
         <v>2</v>
@@ -27126,13 +27131,13 @@
     </row>
     <row r="116" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E116" s="29" t="n">
         <v>20</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G116" s="31" t="n">
         <v>2</v>
@@ -27201,13 +27206,13 @@
     </row>
     <row r="117" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D117" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E117" s="29" t="n">
         <v>29</v>
       </c>
       <c r="F117" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G117" s="31" t="n">
         <v>2</v>
@@ -27276,13 +27281,13 @@
     </row>
     <row r="118" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D118" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E118" s="29" t="n">
         <v>46</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G118" s="31" t="n">
         <v>2</v>
@@ -27351,13 +27356,13 @@
     </row>
     <row r="119" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D119" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E119" s="29" t="n">
         <v>50</v>
       </c>
       <c r="F119" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G119" s="31" t="n">
         <v>2</v>
@@ -27426,13 +27431,13 @@
     </row>
     <row r="120" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E120" s="29" t="n">
         <v>81</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G120" s="31" t="n">
         <v>2</v>
@@ -27501,13 +27506,13 @@
     </row>
     <row r="121" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D121" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E121" s="29" t="n">
         <v>84</v>
       </c>
       <c r="F121" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G121" s="31" t="n">
         <v>2</v>
@@ -27576,13 +27581,13 @@
     </row>
     <row r="122" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D122" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E122" s="29" t="n">
         <v>87</v>
       </c>
       <c r="F122" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G122" s="31" t="n">
         <v>2</v>
@@ -27651,13 +27656,13 @@
     </row>
     <row r="123" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D123" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E123" s="29" t="n">
         <v>18</v>
       </c>
       <c r="F123" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G123" s="31" t="n">
         <v>3</v>
@@ -27726,13 +27731,13 @@
     </row>
     <row r="124" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D124" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E124" s="29" t="n">
         <v>31</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G124" s="31" t="n">
         <v>3</v>
@@ -27801,13 +27806,13 @@
     </row>
     <row r="125" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D125" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E125" s="29" t="n">
         <v>43</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G125" s="31" t="n">
         <v>3</v>
@@ -27876,13 +27881,13 @@
     </row>
     <row r="126" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D126" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E126" s="29" t="n">
         <v>48</v>
       </c>
       <c r="F126" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G126" s="31" t="n">
         <v>3</v>
@@ -27951,13 +27956,13 @@
     </row>
     <row r="127" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E127" s="29" t="n">
         <v>59</v>
       </c>
       <c r="F127" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G127" s="31" t="n">
         <v>3</v>
@@ -28026,13 +28031,13 @@
     </row>
     <row r="128" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E128" s="29" t="n">
         <v>60</v>
       </c>
       <c r="F128" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G128" s="31" t="n">
         <v>3</v>
@@ -28101,13 +28106,13 @@
     </row>
     <row r="129" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D129" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E129" s="29" t="n">
         <v>64</v>
       </c>
       <c r="F129" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G129" s="31" t="n">
         <v>3</v>
@@ -28176,13 +28181,13 @@
     </row>
     <row r="130" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E130" s="29" t="n">
         <v>80</v>
       </c>
       <c r="F130" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G130" s="31" t="n">
         <v>3</v>
@@ -28251,13 +28256,13 @@
     </row>
     <row r="131" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E131" s="29" t="n">
         <v>92</v>
       </c>
       <c r="F131" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G131" s="31" t="n">
         <v>3</v>
@@ -28326,13 +28331,13 @@
     </row>
     <row r="132" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D132" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E132" s="29" t="n">
         <v>95</v>
       </c>
       <c r="F132" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G132" s="31" t="n">
         <v>3</v>
@@ -28401,7 +28406,7 @@
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D133" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E133" s="7" t="n">
         <v>1</v>
@@ -28415,13 +28420,13 @@
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D134" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E134" s="7" t="n">
         <v>9999999</v>
       </c>
       <c r="F134" s="32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -28481,7 +28486,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E1" s="9"/>
       <c r="F1" s="10"/>
@@ -28526,16 +28531,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="16"/>
       <c r="J3" s="17"/>
@@ -28567,7 +28572,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="17"/>
     </row>
@@ -28584,7 +28589,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="19" t="n">
         <f aca="false">(4-D3)*20+1</f>
@@ -28602,7 +28607,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" s="17"/>
     </row>
@@ -28638,7 +28643,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="17"/>
     </row>
@@ -28655,7 +28660,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="19" t="n">
         <f aca="false">E6+1</f>
@@ -28674,7 +28679,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="17"/>
     </row>
@@ -28711,7 +28716,7 @@
         <v>103</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="17"/>
     </row>
@@ -28728,7 +28733,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="19" t="n">
         <f aca="false">E8+1</f>
@@ -28775,7 +28780,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I10" s="17"/>
       <c r="J10" s="17"/>
@@ -28793,7 +28798,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="19" t="n">
         <f aca="false">E10+1</f>
@@ -28859,7 +28864,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">E12+1</f>
@@ -28922,7 +28927,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" s="19" t="n">
         <f aca="false">E14+1</f>
@@ -28982,7 +28987,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E17" s="19" t="n">
         <f aca="false">E16+1</f>
@@ -29048,7 +29053,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="19" t="n">
         <f aca="false">E18+1</f>
@@ -29079,7 +29084,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E20" s="19" t="n">
         <f aca="false">E19+1</f>
@@ -29110,7 +29115,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E21" s="19" t="n">
         <f aca="false">E20+1</f>
@@ -29141,7 +29146,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E22" s="19" t="n">
         <f aca="false">E21+1</f>
@@ -29172,7 +29177,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E23" s="19" t="n">
         <f aca="false">E22+1</f>
@@ -29260,7 +29265,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E26" s="19" t="n">
         <f aca="false">D29</f>
@@ -29291,7 +29296,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E27" s="19" t="n">
         <f aca="false">E26+1</f>
@@ -29322,7 +29327,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E28" s="19" t="n">
         <f aca="false">E27+1</f>
@@ -29423,163 +29428,163 @@
         <v>0</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H32" s="28" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I32" s="28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J32" s="28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K32" s="28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L32" s="28" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M32" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N32" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O32" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P32" s="28" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q32" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R32" s="28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S32" s="28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T32" s="28" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U32" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V32" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W32" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X32" s="28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y32" s="28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z32" s="28" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AA32" s="28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AB32" s="28" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AC32" s="28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AD32" s="28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AE32" s="28" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AF32" s="28" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG32" s="28" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH32" s="28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AI32" s="28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AJ32" s="28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AK32" s="28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AL32" s="28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AM32" s="28" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AN32" s="28" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AO32" s="28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AP32" s="28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AQ32" s="28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AR32" s="28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AS32" s="28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AT32" s="28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AU32" s="28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AV32" s="28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AW32" s="28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AX32" s="28" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AY32" s="28" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ32" s="28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BA32" s="28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BB32" s="28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BC32" s="28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="BD32" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29595,13 +29600,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E33" s="29" t="n">
         <v>7</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G33" s="31" t="n">
         <v>1</v>
@@ -29683,13 +29688,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E34" s="29" t="n">
         <v>17</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G34" s="31" t="n">
         <v>1</v>
@@ -29769,13 +29774,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E35" s="29" t="n">
         <v>23</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G35" s="31" t="n">
         <v>1</v>
@@ -29855,13 +29860,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E36" s="29" t="n">
         <v>51</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G36" s="31" t="n">
         <v>1</v>
@@ -29941,13 +29946,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E37" s="29" t="n">
         <v>58</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G37" s="31" t="n">
         <v>1</v>
@@ -30029,13 +30034,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E38" s="29" t="n">
         <v>65</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G38" s="31" t="n">
         <v>1</v>
@@ -30115,13 +30120,13 @@
         <v>0</v>
       </c>
       <c r="D39" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E39" s="29" t="n">
         <v>67</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G39" s="31" t="n">
         <v>1</v>
@@ -30201,13 +30206,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E40" s="29" t="n">
         <v>73</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G40" s="31" t="n">
         <v>1</v>
@@ -30289,13 +30294,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E41" s="29" t="n">
         <v>74</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G41" s="31" t="n">
         <v>1</v>
@@ -30375,13 +30380,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E42" s="29" t="n">
         <v>91</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G42" s="31" t="n">
         <v>1</v>
@@ -30461,13 +30466,13 @@
         <v>0</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E43" s="29" t="n">
         <v>100</v>
       </c>
       <c r="F43" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G43" s="31" t="n">
         <v>1</v>
@@ -30547,13 +30552,13 @@
         <v>0</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E44" s="29" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G44" s="31" t="n">
         <v>2</v>
@@ -30633,13 +30638,13 @@
         <v>0</v>
       </c>
       <c r="D45" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E45" s="29" t="n">
         <v>13</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G45" s="31" t="n">
         <v>2</v>
@@ -30719,13 +30724,13 @@
         <v>0</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E46" s="29" t="n">
         <v>22</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G46" s="31" t="n">
         <v>2</v>
@@ -30805,13 +30810,13 @@
         <v>0</v>
       </c>
       <c r="D47" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E47" s="29" t="n">
         <v>26</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G47" s="31" t="n">
         <v>2</v>
@@ -30891,13 +30896,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E48" s="29" t="n">
         <v>35</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G48" s="31" t="n">
         <v>2</v>
@@ -30977,13 +30982,13 @@
         <v>0</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E49" s="29" t="n">
         <v>38</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G49" s="31" t="n">
         <v>2</v>
@@ -31063,13 +31068,13 @@
         <v>0</v>
       </c>
       <c r="D50" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E50" s="29" t="n">
         <v>45</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" s="31" t="n">
         <v>2</v>
@@ -31149,13 +31154,13 @@
         <v>0</v>
       </c>
       <c r="D51" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E51" s="29" t="n">
         <v>47</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G51" s="31" t="n">
         <v>2</v>
@@ -31235,13 +31240,13 @@
         <v>0</v>
       </c>
       <c r="D52" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E52" s="29" t="n">
         <v>55</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G52" s="31" t="n">
         <v>2</v>
@@ -31321,13 +31326,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E53" s="29" t="n">
         <v>72</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G53" s="31" t="n">
         <v>2</v>
@@ -31407,13 +31412,13 @@
         <v>0</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E54" s="29" t="n">
         <v>78</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G54" s="31" t="n">
         <v>2</v>
@@ -31493,13 +31498,13 @@
         <v>0</v>
       </c>
       <c r="D55" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E55" s="29" t="n">
         <v>88</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G55" s="31" t="n">
         <v>2</v>
@@ -31579,13 +31584,13 @@
         <v>0</v>
       </c>
       <c r="D56" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E56" s="29" t="n">
         <v>89</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G56" s="31" t="n">
         <v>2</v>
@@ -31665,13 +31670,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E57" s="29" t="n">
         <v>97</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G57" s="31" t="n">
         <v>2</v>
@@ -31751,13 +31756,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E58" s="29" t="n">
         <v>5</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G58" s="31" t="n">
         <v>3</v>
@@ -31837,13 +31842,13 @@
         <v>0</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E59" s="29" t="n">
         <v>12</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G59" s="31" t="n">
         <v>3</v>
@@ -31923,13 +31928,13 @@
         <v>0</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E60" s="29" t="n">
         <v>14</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G60" s="31" t="n">
         <v>3</v>
@@ -32009,13 +32014,13 @@
         <v>0</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E61" s="29" t="n">
         <v>39</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G61" s="31" t="n">
         <v>3</v>
@@ -32095,13 +32100,13 @@
         <v>0</v>
       </c>
       <c r="D62" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E62" s="29" t="n">
         <v>49</v>
       </c>
       <c r="F62" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G62" s="31" t="n">
         <v>3</v>
@@ -32181,13 +32186,13 @@
         <v>0</v>
       </c>
       <c r="D63" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E63" s="29" t="n">
         <v>62</v>
       </c>
       <c r="F63" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G63" s="31" t="n">
         <v>3</v>
@@ -32267,13 +32272,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E64" s="29" t="n">
         <v>79</v>
       </c>
       <c r="F64" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G64" s="31" t="n">
         <v>3</v>
@@ -32353,13 +32358,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E65" s="29" t="n">
         <v>98</v>
       </c>
       <c r="F65" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G65" s="31" t="n">
         <v>3</v>
@@ -32439,13 +32444,13 @@
         <v>0</v>
       </c>
       <c r="D66" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E66" s="29" t="n">
         <v>8</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G66" s="31" t="n">
         <v>1</v>
@@ -32525,13 +32530,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E67" s="29" t="n">
         <v>9</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G67" s="31" t="n">
         <v>1</v>
@@ -32611,13 +32616,13 @@
         <v>0</v>
       </c>
       <c r="D68" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E68" s="29" t="n">
         <v>24</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G68" s="31" t="n">
         <v>1</v>
@@ -32697,13 +32702,13 @@
         <v>0</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E69" s="29" t="n">
         <v>30</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G69" s="31" t="n">
         <v>1</v>
@@ -32783,13 +32788,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E70" s="29" t="n">
         <v>32</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G70" s="31" t="n">
         <v>1</v>
@@ -32869,13 +32874,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E71" s="29" t="n">
         <v>36</v>
       </c>
       <c r="F71" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G71" s="31" t="n">
         <v>1</v>
@@ -32955,13 +32960,13 @@
         <v>0</v>
       </c>
       <c r="D72" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E72" s="29" t="n">
         <v>53</v>
       </c>
       <c r="F72" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G72" s="31" t="n">
         <v>1</v>
@@ -33041,13 +33046,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E73" s="29" t="n">
         <v>61</v>
       </c>
       <c r="F73" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G73" s="31" t="n">
         <v>1</v>
@@ -33127,13 +33132,13 @@
         <v>0</v>
       </c>
       <c r="D74" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E74" s="29" t="n">
         <v>70</v>
       </c>
       <c r="F74" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G74" s="31" t="n">
         <v>1</v>
@@ -33213,13 +33218,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E75" s="29" t="n">
         <v>4</v>
       </c>
       <c r="F75" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G75" s="31" t="n">
         <v>2</v>
@@ -33299,13 +33304,13 @@
         <v>0</v>
       </c>
       <c r="D76" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E76" s="29" t="n">
         <v>6</v>
       </c>
       <c r="F76" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G76" s="31" t="n">
         <v>2</v>
@@ -33385,13 +33390,13 @@
         <v>0</v>
       </c>
       <c r="D77" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E77" s="29" t="n">
         <v>19</v>
       </c>
       <c r="F77" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G77" s="31" t="n">
         <v>2</v>
@@ -33471,13 +33476,13 @@
         <v>0</v>
       </c>
       <c r="D78" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E78" s="29" t="n">
         <v>25</v>
       </c>
       <c r="F78" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G78" s="31" t="n">
         <v>2</v>
@@ -33557,13 +33562,13 @@
         <v>0</v>
       </c>
       <c r="D79" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E79" s="29" t="n">
         <v>28</v>
       </c>
       <c r="F79" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G79" s="31" t="n">
         <v>2</v>
@@ -33643,13 +33648,13 @@
         <v>0</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E80" s="29" t="n">
         <v>34</v>
       </c>
       <c r="F80" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G80" s="31" t="n">
         <v>2</v>
@@ -33729,13 +33734,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E81" s="29" t="n">
         <v>44</v>
       </c>
       <c r="F81" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G81" s="31" t="n">
         <v>2</v>
@@ -33815,13 +33820,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E82" s="29" t="n">
         <v>52</v>
       </c>
       <c r="F82" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G82" s="31" t="n">
         <v>2</v>
@@ -33901,13 +33906,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E83" s="29" t="n">
         <v>54</v>
       </c>
       <c r="F83" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G83" s="31" t="n">
         <v>2</v>
@@ -33987,13 +33992,13 @@
         <v>0</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E84" s="29" t="n">
         <v>56</v>
       </c>
       <c r="F84" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G84" s="31" t="n">
         <v>2</v>
@@ -34073,13 +34078,13 @@
         <v>0</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E85" s="29" t="n">
         <v>57</v>
       </c>
       <c r="F85" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G85" s="31" t="n">
         <v>2</v>
@@ -34159,13 +34164,13 @@
         <v>0</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E86" s="29" t="n">
         <v>66</v>
       </c>
       <c r="F86" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G86" s="31" t="n">
         <v>2</v>
@@ -34245,13 +34250,13 @@
         <v>0</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E87" s="29" t="n">
         <v>71</v>
       </c>
       <c r="F87" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G87" s="31" t="n">
         <v>2</v>
@@ -34331,13 +34336,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E88" s="29" t="n">
         <v>77</v>
       </c>
       <c r="F88" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G88" s="31" t="n">
         <v>2</v>
@@ -34417,13 +34422,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E89" s="29" t="n">
         <v>83</v>
       </c>
       <c r="F89" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G89" s="31" t="n">
         <v>2</v>
@@ -34503,13 +34508,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E90" s="29" t="n">
         <v>85</v>
       </c>
       <c r="F90" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G90" s="31" t="n">
         <v>2</v>
@@ -34589,13 +34594,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E91" s="29" t="n">
         <v>90</v>
       </c>
       <c r="F91" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G91" s="31" t="n">
         <v>2</v>
@@ -34675,13 +34680,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E92" s="29" t="n">
         <v>94</v>
       </c>
       <c r="F92" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G92" s="31" t="n">
         <v>2</v>
@@ -34761,13 +34766,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E93" s="29" t="n">
         <v>96</v>
       </c>
       <c r="F93" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G93" s="31" t="n">
         <v>2</v>
@@ -34847,13 +34852,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E94" s="29" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G94" s="31" t="n">
         <v>3</v>
@@ -34933,13 +34938,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E95" s="29" t="n">
         <v>15</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G95" s="31" t="n">
         <v>3</v>
@@ -35019,13 +35024,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E96" s="29" t="n">
         <v>21</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G96" s="31" t="n">
         <v>3</v>
@@ -35105,13 +35110,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E97" s="29" t="n">
         <v>27</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G97" s="31" t="n">
         <v>3</v>
@@ -35191,13 +35196,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E98" s="29" t="n">
         <v>37</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G98" s="31" t="n">
         <v>3</v>
@@ -35277,13 +35282,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E99" s="29" t="n">
         <v>40</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G99" s="31" t="n">
         <v>3</v>
@@ -35363,13 +35368,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E100" s="29" t="n">
         <v>63</v>
       </c>
       <c r="F100" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G100" s="31" t="n">
         <v>3</v>
@@ -35438,13 +35443,13 @@
     </row>
     <row r="101" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D101" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E101" s="29" t="n">
         <v>69</v>
       </c>
       <c r="F101" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G101" s="31" t="n">
         <v>3</v>
@@ -35513,13 +35518,13 @@
     </row>
     <row r="102" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D102" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E102" s="29" t="n">
         <v>76</v>
       </c>
       <c r="F102" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G102" s="31" t="n">
         <v>3</v>
@@ -35588,13 +35593,13 @@
     </row>
     <row r="103" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D103" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E103" s="29" t="n">
         <v>99</v>
       </c>
       <c r="F103" s="30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G103" s="31" t="n">
         <v>3</v>
@@ -35663,13 +35668,13 @@
     </row>
     <row r="104" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E104" s="29" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G104" s="31" t="n">
         <v>1</v>
@@ -35738,13 +35743,13 @@
     </row>
     <row r="105" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E105" s="29" t="n">
         <v>10</v>
       </c>
       <c r="F105" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G105" s="31" t="n">
         <v>1</v>
@@ -35813,13 +35818,13 @@
     </row>
     <row r="106" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D106" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E106" s="29" t="n">
         <v>16</v>
       </c>
       <c r="F106" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G106" s="31" t="n">
         <v>1</v>
@@ -35888,13 +35893,13 @@
     </row>
     <row r="107" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E107" s="29" t="n">
         <v>33</v>
       </c>
       <c r="F107" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G107" s="31" t="n">
         <v>1</v>
@@ -35963,13 +35968,13 @@
     </row>
     <row r="108" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D108" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E108" s="29" t="n">
         <v>41</v>
       </c>
       <c r="F108" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G108" s="31" t="n">
         <v>1</v>
@@ -36038,13 +36043,13 @@
     </row>
     <row r="109" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D109" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E109" s="29" t="n">
         <v>42</v>
       </c>
       <c r="F109" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G109" s="31" t="n">
         <v>1</v>
@@ -36113,13 +36118,13 @@
     </row>
     <row r="110" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D110" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E110" s="29" t="n">
         <v>68</v>
       </c>
       <c r="F110" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G110" s="31" t="n">
         <v>1</v>
@@ -36188,13 +36193,13 @@
     </row>
     <row r="111" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D111" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E111" s="29" t="n">
         <v>75</v>
       </c>
       <c r="F111" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G111" s="31" t="n">
         <v>1</v>
@@ -36263,13 +36268,13 @@
     </row>
     <row r="112" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E112" s="29" t="n">
         <v>82</v>
       </c>
       <c r="F112" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G112" s="31" t="n">
         <v>1</v>
@@ -36338,13 +36343,13 @@
     </row>
     <row r="113" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D113" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E113" s="29" t="n">
         <v>86</v>
       </c>
       <c r="F113" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G113" s="31" t="n">
         <v>1</v>
@@ -36413,13 +36418,13 @@
     </row>
     <row r="114" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D114" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E114" s="29" t="n">
         <v>93</v>
       </c>
       <c r="F114" s="30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G114" s="31" t="n">
         <v>1</v>
@@ -36488,13 +36493,13 @@
     </row>
     <row r="115" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D115" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E115" s="29" t="n">
         <v>11</v>
       </c>
       <c r="F115" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G115" s="31" t="n">
         <v>2</v>
@@ -36563,13 +36568,13 @@
     </row>
     <row r="116" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E116" s="29" t="n">
         <v>20</v>
       </c>
       <c r="F116" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G116" s="31" t="n">
         <v>2</v>
@@ -36638,13 +36643,13 @@
     </row>
     <row r="117" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D117" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E117" s="29" t="n">
         <v>29</v>
       </c>
       <c r="F117" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G117" s="31" t="n">
         <v>2</v>
@@ -36713,13 +36718,13 @@
     </row>
     <row r="118" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D118" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E118" s="29" t="n">
         <v>46</v>
       </c>
       <c r="F118" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G118" s="31" t="n">
         <v>2</v>
@@ -36788,13 +36793,13 @@
     </row>
     <row r="119" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D119" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E119" s="29" t="n">
         <v>50</v>
       </c>
       <c r="F119" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G119" s="31" t="n">
         <v>2</v>
@@ -36863,13 +36868,13 @@
     </row>
     <row r="120" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E120" s="29" t="n">
         <v>81</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G120" s="31" t="n">
         <v>2</v>
@@ -36938,13 +36943,13 @@
     </row>
     <row r="121" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D121" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E121" s="29" t="n">
         <v>84</v>
       </c>
       <c r="F121" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G121" s="31" t="n">
         <v>2</v>
@@ -37013,13 +37018,13 @@
     </row>
     <row r="122" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D122" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E122" s="29" t="n">
         <v>87</v>
       </c>
       <c r="F122" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G122" s="31" t="n">
         <v>2</v>
@@ -37088,13 +37093,13 @@
     </row>
     <row r="123" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D123" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E123" s="29" t="n">
         <v>18</v>
       </c>
       <c r="F123" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G123" s="31" t="n">
         <v>3</v>
@@ -37163,13 +37168,13 @@
     </row>
     <row r="124" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D124" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E124" s="29" t="n">
         <v>31</v>
       </c>
       <c r="F124" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G124" s="31" t="n">
         <v>3</v>
@@ -37238,13 +37243,13 @@
     </row>
     <row r="125" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D125" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E125" s="29" t="n">
         <v>43</v>
       </c>
       <c r="F125" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G125" s="31" t="n">
         <v>3</v>
@@ -37313,13 +37318,13 @@
     </row>
     <row r="126" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D126" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E126" s="29" t="n">
         <v>48</v>
       </c>
       <c r="F126" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G126" s="31" t="n">
         <v>3</v>
@@ -37388,13 +37393,13 @@
     </row>
     <row r="127" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E127" s="29" t="n">
         <v>59</v>
       </c>
       <c r="F127" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G127" s="31" t="n">
         <v>3</v>
@@ -37463,13 +37468,13 @@
     </row>
     <row r="128" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E128" s="29" t="n">
         <v>60</v>
       </c>
       <c r="F128" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G128" s="31" t="n">
         <v>3</v>
@@ -37538,13 +37543,13 @@
     </row>
     <row r="129" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D129" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E129" s="29" t="n">
         <v>64</v>
       </c>
       <c r="F129" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G129" s="31" t="n">
         <v>3</v>
@@ -37613,13 +37618,13 @@
     </row>
     <row r="130" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E130" s="29" t="n">
         <v>80</v>
       </c>
       <c r="F130" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G130" s="31" t="n">
         <v>3</v>
@@ -37688,13 +37693,13 @@
     </row>
     <row r="131" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E131" s="29" t="n">
         <v>92</v>
       </c>
       <c r="F131" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G131" s="31" t="n">
         <v>3</v>
@@ -37763,13 +37768,13 @@
     </row>
     <row r="132" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D132" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E132" s="29" t="n">
         <v>95</v>
       </c>
       <c r="F132" s="30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G132" s="31" t="n">
         <v>3</v>

--- a/inst/extdata/Verbatims_fake_survey.xlsx
+++ b/inst/extdata/Verbatims_fake_survey.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Codestufen" sheetId="1" state="visible" r:id="rId2"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="116">
   <si>
     <t xml:space="preserve">love </t>
   </si>
@@ -104,10 +104,13 @@
     <t xml:space="preserve">fear</t>
   </si>
   <si>
-    <t xml:space="preserve">happiness</t>
+    <t xml:space="preserve"> happiness</t>
   </si>
   <si>
     <t xml:space="preserve">anger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">happiness</t>
   </si>
   <si>
     <t xml:space="preserve">pain</t>
@@ -1029,10 +1032,10 @@
         <v>5</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1042,13 +1045,13 @@
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1057,7 +1060,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -1979,16 +1982,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2007,16 +2010,16 @@
         <v>99</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7467,7 +7470,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1" s="8"/>
       <c r="F1" s="9"/>
@@ -7502,7 +7505,7 @@
       </c>
       <c r="B3" s="6" t="str">
         <f aca="false">Codestufen!B4</f>
-        <v>happiness</v>
+        <v> happiness</v>
       </c>
       <c r="C3" s="6" t="n">
         <f aca="false">COUNTIF(V_W_Q6_Zuord,A3)</f>
@@ -7512,16 +7515,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="15"/>
       <c r="J3" s="16"/>
@@ -7553,7 +7556,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="16"/>
     </row>
@@ -7570,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">(4-D3)*20+1</f>
@@ -7588,7 +7591,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="16"/>
     </row>
@@ -7624,7 +7627,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="16"/>
     </row>
@@ -7641,7 +7644,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">E6+1</f>
@@ -7649,7 +7652,7 @@
       </c>
       <c r="F7" s="19" t="str">
         <f aca="false">HYPERLINK("#Codestufen!"&amp;ADDRESS(E7+1,D$6),IF(INDEX(V_W_Q6_CodestufenName,E7)=0,"",INDEX(V_W_Q6_CodestufenName,E7)))</f>
-        <v>happiness</v>
+        <v> happiness</v>
       </c>
       <c r="G7" s="18" t="n">
         <f aca="false">INDEX(V_W_Q6_Codestufen,E7)</f>
@@ -7660,7 +7663,7 @@
         <v>96</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7" s="16"/>
     </row>
@@ -7697,7 +7700,7 @@
         <v>96</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" s="16"/>
     </row>
@@ -7714,7 +7717,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">E8+1</f>
@@ -7761,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
@@ -7779,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">E10+1</f>
@@ -7845,7 +7848,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">E12+1</f>
@@ -7908,7 +7911,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="18" t="n">
         <f aca="false">E14+1</f>
@@ -7968,7 +7971,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">E16+1</f>
@@ -8034,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="18" t="n">
         <f aca="false">E18+1</f>
@@ -8065,7 +8068,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E20" s="18" t="n">
         <f aca="false">E19+1</f>
@@ -8096,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">E20+1</f>
@@ -8127,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">E21+1</f>
@@ -8158,7 +8161,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" s="18" t="n">
         <f aca="false">E22+1</f>
@@ -8246,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" s="18" t="n">
         <f aca="false">D29</f>
@@ -8277,7 +8280,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E27" s="18" t="n">
         <f aca="false">E26+1</f>
@@ -8308,7 +8311,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">E27+1</f>
@@ -8409,55 +8412,55 @@
         <v>0</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G32" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H32" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J32" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K32" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L32" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M32" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N32" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O32" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P32" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q32" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R32" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S32" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T32" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8473,13 +8476,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E33" s="28" t="n">
         <v>7</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G33" s="30" t="n">
         <v>1</v>
@@ -8523,13 +8526,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E34" s="28" t="n">
         <v>17</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G34" s="30" t="n">
         <v>1</v>
@@ -8573,13 +8576,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E35" s="28" t="n">
         <v>23</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G35" s="30" t="n">
         <v>1</v>
@@ -8623,13 +8626,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E36" s="28" t="n">
         <v>51</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G36" s="30" t="n">
         <v>1</v>
@@ -8673,13 +8676,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E37" s="28" t="n">
         <v>58</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G37" s="30" t="n">
         <v>1</v>
@@ -8723,13 +8726,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E38" s="28" t="n">
         <v>65</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G38" s="30" t="n">
         <v>1</v>
@@ -8773,13 +8776,13 @@
         <v>0</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E39" s="28" t="n">
         <v>67</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G39" s="30" t="n">
         <v>1</v>
@@ -8823,13 +8826,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E40" s="28" t="n">
         <v>73</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G40" s="30" t="n">
         <v>1</v>
@@ -8873,13 +8876,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E41" s="28" t="n">
         <v>74</v>
       </c>
       <c r="F41" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G41" s="30" t="n">
         <v>1</v>
@@ -8923,13 +8926,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E42" s="28" t="n">
         <v>91</v>
       </c>
       <c r="F42" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G42" s="30" t="n">
         <v>1</v>
@@ -8973,13 +8976,13 @@
         <v>0</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E43" s="28" t="n">
         <v>100</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G43" s="30" t="n">
         <v>1</v>
@@ -9023,13 +9026,13 @@
         <v>0</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E44" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G44" s="30" t="n">
         <v>2</v>
@@ -9073,13 +9076,13 @@
         <v>0</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E45" s="28" t="n">
         <v>13</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G45" s="30" t="n">
         <v>2</v>
@@ -9123,13 +9126,13 @@
         <v>0</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E46" s="28" t="n">
         <v>22</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G46" s="30" t="n">
         <v>2</v>
@@ -9173,13 +9176,13 @@
         <v>0</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E47" s="28" t="n">
         <v>26</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G47" s="30" t="n">
         <v>2</v>
@@ -9223,13 +9226,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E48" s="28" t="n">
         <v>35</v>
       </c>
       <c r="F48" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G48" s="30" t="n">
         <v>2</v>
@@ -9273,13 +9276,13 @@
         <v>0</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E49" s="28" t="n">
         <v>38</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G49" s="30" t="n">
         <v>2</v>
@@ -9323,13 +9326,13 @@
         <v>0</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E50" s="28" t="n">
         <v>45</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G50" s="30" t="n">
         <v>2</v>
@@ -9373,13 +9376,13 @@
         <v>0</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E51" s="28" t="n">
         <v>47</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G51" s="30" t="n">
         <v>2</v>
@@ -9423,13 +9426,13 @@
         <v>0</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E52" s="28" t="n">
         <v>55</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G52" s="30" t="n">
         <v>2</v>
@@ -9473,13 +9476,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E53" s="28" t="n">
         <v>72</v>
       </c>
       <c r="F53" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G53" s="30" t="n">
         <v>2</v>
@@ -9523,13 +9526,13 @@
         <v>0</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E54" s="28" t="n">
         <v>78</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G54" s="30" t="n">
         <v>2</v>
@@ -9573,13 +9576,13 @@
         <v>0</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E55" s="28" t="n">
         <v>88</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G55" s="30" t="n">
         <v>2</v>
@@ -9623,13 +9626,13 @@
         <v>0</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E56" s="28" t="n">
         <v>89</v>
       </c>
       <c r="F56" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G56" s="30" t="n">
         <v>2</v>
@@ -9673,13 +9676,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E57" s="28" t="n">
         <v>97</v>
       </c>
       <c r="F57" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G57" s="30" t="n">
         <v>2</v>
@@ -9723,13 +9726,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E58" s="28" t="n">
         <v>5</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G58" s="30" t="n">
         <v>3</v>
@@ -9773,13 +9776,13 @@
         <v>0</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E59" s="28" t="n">
         <v>12</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G59" s="30" t="n">
         <v>3</v>
@@ -9823,13 +9826,13 @@
         <v>0</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E60" s="28" t="n">
         <v>14</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G60" s="30" t="n">
         <v>3</v>
@@ -9873,13 +9876,13 @@
         <v>0</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E61" s="28" t="n">
         <v>39</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G61" s="30" t="n">
         <v>3</v>
@@ -9923,13 +9926,13 @@
         <v>0</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E62" s="28" t="n">
         <v>49</v>
       </c>
       <c r="F62" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G62" s="30" t="n">
         <v>3</v>
@@ -9973,13 +9976,13 @@
         <v>0</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E63" s="28" t="n">
         <v>62</v>
       </c>
       <c r="F63" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G63" s="30" t="n">
         <v>3</v>
@@ -10023,13 +10026,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E64" s="28" t="n">
         <v>79</v>
       </c>
       <c r="F64" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G64" s="30" t="n">
         <v>3</v>
@@ -10073,13 +10076,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E65" s="28" t="n">
         <v>98</v>
       </c>
       <c r="F65" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G65" s="30" t="n">
         <v>3</v>
@@ -10123,13 +10126,13 @@
         <v>0</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E66" s="28" t="n">
         <v>8</v>
       </c>
       <c r="F66" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G66" s="30" t="n">
         <v>1</v>
@@ -10173,13 +10176,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E67" s="28" t="n">
         <v>9</v>
       </c>
       <c r="F67" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G67" s="30" t="n">
         <v>1</v>
@@ -10223,13 +10226,13 @@
         <v>0</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E68" s="28" t="n">
         <v>24</v>
       </c>
       <c r="F68" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G68" s="30" t="n">
         <v>1</v>
@@ -10273,13 +10276,13 @@
         <v>0</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E69" s="28" t="n">
         <v>30</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G69" s="30" t="n">
         <v>1</v>
@@ -10323,13 +10326,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E70" s="28" t="n">
         <v>32</v>
       </c>
       <c r="F70" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G70" s="30" t="n">
         <v>1</v>
@@ -10373,13 +10376,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E71" s="28" t="n">
         <v>36</v>
       </c>
       <c r="F71" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G71" s="30" t="n">
         <v>1</v>
@@ -10423,13 +10426,13 @@
         <v>0</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E72" s="28" t="n">
         <v>53</v>
       </c>
       <c r="F72" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G72" s="30" t="n">
         <v>1</v>
@@ -10473,13 +10476,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E73" s="28" t="n">
         <v>61</v>
       </c>
       <c r="F73" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G73" s="30" t="n">
         <v>1</v>
@@ -10523,13 +10526,13 @@
         <v>0</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E74" s="28" t="n">
         <v>70</v>
       </c>
       <c r="F74" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G74" s="30" t="n">
         <v>1</v>
@@ -10573,13 +10576,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E75" s="28" t="n">
         <v>4</v>
       </c>
       <c r="F75" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G75" s="30" t="n">
         <v>2</v>
@@ -10623,13 +10626,13 @@
         <v>0</v>
       </c>
       <c r="D76" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E76" s="28" t="n">
         <v>6</v>
       </c>
       <c r="F76" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G76" s="30" t="n">
         <v>2</v>
@@ -10673,13 +10676,13 @@
         <v>0</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E77" s="28" t="n">
         <v>19</v>
       </c>
       <c r="F77" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G77" s="30" t="n">
         <v>2</v>
@@ -10723,13 +10726,13 @@
         <v>0</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E78" s="28" t="n">
         <v>25</v>
       </c>
       <c r="F78" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G78" s="30" t="n">
         <v>2</v>
@@ -10773,13 +10776,13 @@
         <v>0</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E79" s="28" t="n">
         <v>28</v>
       </c>
       <c r="F79" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G79" s="30" t="n">
         <v>2</v>
@@ -10823,13 +10826,13 @@
         <v>0</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E80" s="28" t="n">
         <v>34</v>
       </c>
       <c r="F80" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G80" s="30" t="n">
         <v>2</v>
@@ -10873,13 +10876,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E81" s="28" t="n">
         <v>44</v>
       </c>
       <c r="F81" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G81" s="30" t="n">
         <v>2</v>
@@ -10923,13 +10926,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E82" s="28" t="n">
         <v>52</v>
       </c>
       <c r="F82" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G82" s="30" t="n">
         <v>2</v>
@@ -10973,13 +10976,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E83" s="28" t="n">
         <v>54</v>
       </c>
       <c r="F83" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G83" s="30" t="n">
         <v>2</v>
@@ -11023,13 +11026,13 @@
         <v>0</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E84" s="28" t="n">
         <v>56</v>
       </c>
       <c r="F84" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G84" s="30" t="n">
         <v>2</v>
@@ -11073,13 +11076,13 @@
         <v>0</v>
       </c>
       <c r="D85" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E85" s="28" t="n">
         <v>57</v>
       </c>
       <c r="F85" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G85" s="30" t="n">
         <v>2</v>
@@ -11123,13 +11126,13 @@
         <v>0</v>
       </c>
       <c r="D86" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E86" s="28" t="n">
         <v>66</v>
       </c>
       <c r="F86" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G86" s="30" t="n">
         <v>2</v>
@@ -11173,13 +11176,13 @@
         <v>0</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E87" s="28" t="n">
         <v>71</v>
       </c>
       <c r="F87" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G87" s="30" t="n">
         <v>2</v>
@@ -11223,13 +11226,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E88" s="28" t="n">
         <v>77</v>
       </c>
       <c r="F88" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G88" s="30" t="n">
         <v>2</v>
@@ -11273,13 +11276,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E89" s="28" t="n">
         <v>83</v>
       </c>
       <c r="F89" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G89" s="30" t="n">
         <v>2</v>
@@ -11323,13 +11326,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E90" s="28" t="n">
         <v>85</v>
       </c>
       <c r="F90" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G90" s="30" t="n">
         <v>2</v>
@@ -11373,13 +11376,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E91" s="28" t="n">
         <v>90</v>
       </c>
       <c r="F91" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G91" s="30" t="n">
         <v>2</v>
@@ -11423,13 +11426,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E92" s="28" t="n">
         <v>94</v>
       </c>
       <c r="F92" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G92" s="30" t="n">
         <v>2</v>
@@ -11473,13 +11476,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E93" s="28" t="n">
         <v>96</v>
       </c>
       <c r="F93" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G93" s="30" t="n">
         <v>2</v>
@@ -11523,13 +11526,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E94" s="28" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G94" s="30" t="n">
         <v>3</v>
@@ -11573,13 +11576,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E95" s="28" t="n">
         <v>15</v>
       </c>
       <c r="F95" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G95" s="30" t="n">
         <v>3</v>
@@ -11623,13 +11626,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E96" s="28" t="n">
         <v>21</v>
       </c>
       <c r="F96" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G96" s="30" t="n">
         <v>3</v>
@@ -11673,13 +11676,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E97" s="28" t="n">
         <v>27</v>
       </c>
       <c r="F97" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G97" s="30" t="n">
         <v>3</v>
@@ -11723,13 +11726,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E98" s="28" t="n">
         <v>37</v>
       </c>
       <c r="F98" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G98" s="30" t="n">
         <v>3</v>
@@ -11773,13 +11776,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E99" s="28" t="n">
         <v>40</v>
       </c>
       <c r="F99" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G99" s="30" t="n">
         <v>3</v>
@@ -11823,13 +11826,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E100" s="28" t="n">
         <v>63</v>
       </c>
       <c r="F100" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G100" s="30" t="n">
         <v>3</v>
@@ -11862,13 +11865,13 @@
     </row>
     <row r="101" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D101" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E101" s="28" t="n">
         <v>69</v>
       </c>
       <c r="F101" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G101" s="30" t="n">
         <v>3</v>
@@ -11901,13 +11904,13 @@
     </row>
     <row r="102" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D102" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E102" s="28" t="n">
         <v>76</v>
       </c>
       <c r="F102" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G102" s="30" t="n">
         <v>3</v>
@@ -11940,13 +11943,13 @@
     </row>
     <row r="103" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D103" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E103" s="28" t="n">
         <v>99</v>
       </c>
       <c r="F103" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G103" s="30" t="n">
         <v>3</v>
@@ -11979,13 +11982,13 @@
     </row>
     <row r="104" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E104" s="28" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G104" s="30" t="n">
         <v>1</v>
@@ -12018,13 +12021,13 @@
     </row>
     <row r="105" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E105" s="28" t="n">
         <v>10</v>
       </c>
       <c r="F105" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G105" s="30" t="n">
         <v>1</v>
@@ -12057,13 +12060,13 @@
     </row>
     <row r="106" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D106" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E106" s="28" t="n">
         <v>16</v>
       </c>
       <c r="F106" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G106" s="30" t="n">
         <v>1</v>
@@ -12096,13 +12099,13 @@
     </row>
     <row r="107" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E107" s="28" t="n">
         <v>33</v>
       </c>
       <c r="F107" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G107" s="30" t="n">
         <v>1</v>
@@ -12135,13 +12138,13 @@
     </row>
     <row r="108" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D108" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E108" s="28" t="n">
         <v>41</v>
       </c>
       <c r="F108" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G108" s="30" t="n">
         <v>1</v>
@@ -12174,13 +12177,13 @@
     </row>
     <row r="109" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D109" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E109" s="28" t="n">
         <v>42</v>
       </c>
       <c r="F109" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G109" s="30" t="n">
         <v>1</v>
@@ -12213,13 +12216,13 @@
     </row>
     <row r="110" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D110" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E110" s="28" t="n">
         <v>68</v>
       </c>
       <c r="F110" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G110" s="30" t="n">
         <v>1</v>
@@ -12252,13 +12255,13 @@
     </row>
     <row r="111" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D111" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E111" s="28" t="n">
         <v>75</v>
       </c>
       <c r="F111" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G111" s="30" t="n">
         <v>1</v>
@@ -12291,13 +12294,13 @@
     </row>
     <row r="112" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E112" s="28" t="n">
         <v>82</v>
       </c>
       <c r="F112" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G112" s="30" t="n">
         <v>1</v>
@@ -12330,13 +12333,13 @@
     </row>
     <row r="113" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D113" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E113" s="28" t="n">
         <v>86</v>
       </c>
       <c r="F113" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G113" s="30" t="n">
         <v>1</v>
@@ -12369,13 +12372,13 @@
     </row>
     <row r="114" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D114" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E114" s="28" t="n">
         <v>93</v>
       </c>
       <c r="F114" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G114" s="30" t="n">
         <v>1</v>
@@ -12408,13 +12411,13 @@
     </row>
     <row r="115" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D115" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E115" s="28" t="n">
         <v>11</v>
       </c>
       <c r="F115" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G115" s="30" t="n">
         <v>2</v>
@@ -12447,13 +12450,13 @@
     </row>
     <row r="116" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E116" s="28" t="n">
         <v>20</v>
       </c>
       <c r="F116" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G116" s="30" t="n">
         <v>2</v>
@@ -12486,13 +12489,13 @@
     </row>
     <row r="117" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D117" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E117" s="28" t="n">
         <v>29</v>
       </c>
       <c r="F117" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G117" s="30" t="n">
         <v>2</v>
@@ -12525,13 +12528,13 @@
     </row>
     <row r="118" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D118" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E118" s="28" t="n">
         <v>46</v>
       </c>
       <c r="F118" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G118" s="30" t="n">
         <v>2</v>
@@ -12564,13 +12567,13 @@
     </row>
     <row r="119" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D119" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E119" s="28" t="n">
         <v>50</v>
       </c>
       <c r="F119" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G119" s="30" t="n">
         <v>2</v>
@@ -12603,13 +12606,13 @@
     </row>
     <row r="120" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E120" s="28" t="n">
         <v>81</v>
       </c>
       <c r="F120" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G120" s="30" t="n">
         <v>2</v>
@@ -12642,13 +12645,13 @@
     </row>
     <row r="121" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D121" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E121" s="28" t="n">
         <v>84</v>
       </c>
       <c r="F121" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G121" s="30" t="n">
         <v>2</v>
@@ -12681,13 +12684,13 @@
     </row>
     <row r="122" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D122" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E122" s="28" t="n">
         <v>87</v>
       </c>
       <c r="F122" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G122" s="30" t="n">
         <v>2</v>
@@ -12720,13 +12723,13 @@
     </row>
     <row r="123" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D123" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E123" s="28" t="n">
         <v>18</v>
       </c>
       <c r="F123" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G123" s="30" t="n">
         <v>3</v>
@@ -12759,13 +12762,13 @@
     </row>
     <row r="124" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D124" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E124" s="28" t="n">
         <v>31</v>
       </c>
       <c r="F124" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G124" s="30" t="n">
         <v>3</v>
@@ -12798,13 +12801,13 @@
     </row>
     <row r="125" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D125" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E125" s="28" t="n">
         <v>43</v>
       </c>
       <c r="F125" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G125" s="30" t="n">
         <v>3</v>
@@ -12837,13 +12840,13 @@
     </row>
     <row r="126" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D126" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E126" s="28" t="n">
         <v>48</v>
       </c>
       <c r="F126" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G126" s="30" t="n">
         <v>3</v>
@@ -12876,13 +12879,13 @@
     </row>
     <row r="127" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E127" s="28" t="n">
         <v>59</v>
       </c>
       <c r="F127" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G127" s="30" t="n">
         <v>3</v>
@@ -12915,13 +12918,13 @@
     </row>
     <row r="128" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E128" s="28" t="n">
         <v>60</v>
       </c>
       <c r="F128" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G128" s="30" t="n">
         <v>3</v>
@@ -12954,13 +12957,13 @@
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D129" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E129" s="28" t="n">
         <v>64</v>
       </c>
       <c r="F129" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G129" s="30"/>
       <c r="H129" s="28" t="n">
@@ -12991,13 +12994,13 @@
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E130" s="28" t="n">
         <v>80</v>
       </c>
       <c r="F130" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G130" s="30"/>
       <c r="H130" s="28" t="n">
@@ -13028,13 +13031,13 @@
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E131" s="28" t="n">
         <v>92</v>
       </c>
       <c r="F131" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G131" s="30"/>
       <c r="H131" s="28" t="n">
@@ -13065,13 +13068,13 @@
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D132" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E132" s="28" t="n">
         <v>95</v>
       </c>
       <c r="F132" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G132" s="30"/>
       <c r="H132" s="28" t="n">
@@ -13158,7 +13161,7 @@
         <v>19</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="8"/>
       <c r="F1" s="9"/>
@@ -13203,16 +13206,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="15"/>
       <c r="J3" s="16"/>
@@ -13244,7 +13247,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="16"/>
     </row>
@@ -13261,7 +13264,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">(4-D3)*20+1</f>
@@ -13279,7 +13282,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="16"/>
     </row>
@@ -13315,7 +13318,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="16"/>
     </row>
@@ -13332,7 +13335,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">E6+1</f>
@@ -13351,7 +13354,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7" s="16"/>
     </row>
@@ -13388,7 +13391,7 @@
         <v>100</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" s="16"/>
     </row>
@@ -13405,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">E8+1</f>
@@ -13452,7 +13455,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
@@ -13470,7 +13473,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">E10+1</f>
@@ -13536,7 +13539,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">E12+1</f>
@@ -13599,7 +13602,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="18" t="n">
         <f aca="false">E14+1</f>
@@ -13659,7 +13662,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">E16+1</f>
@@ -13725,7 +13728,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="18" t="n">
         <f aca="false">E18+1</f>
@@ -13756,7 +13759,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E20" s="18" t="n">
         <f aca="false">E19+1</f>
@@ -13787,7 +13790,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">E20+1</f>
@@ -13818,7 +13821,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">E21+1</f>
@@ -13849,7 +13852,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" s="18" t="n">
         <f aca="false">E22+1</f>
@@ -13937,7 +13940,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" s="18" t="n">
         <f aca="false">D29</f>
@@ -13968,7 +13971,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E27" s="18" t="n">
         <f aca="false">E26+1</f>
@@ -13999,7 +14002,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">E27+1</f>
@@ -14100,55 +14103,55 @@
         <v>0</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G32" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H32" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J32" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K32" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L32" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M32" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N32" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O32" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P32" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q32" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R32" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S32" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T32" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14164,13 +14167,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E33" s="28" t="n">
         <v>77</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G33" s="30" t="n">
         <v>1</v>
@@ -14214,13 +14217,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E34" s="28" t="n">
         <v>87</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G34" s="30" t="n">
         <v>1</v>
@@ -14264,13 +14267,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E35" s="28" t="n">
         <v>6</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G35" s="30" t="n">
         <v>4</v>
@@ -14314,13 +14317,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E36" s="28" t="n">
         <v>15</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G36" s="30" t="n">
         <v>4</v>
@@ -14364,13 +14367,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E37" s="28" t="n">
         <v>23</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G37" s="30" t="n">
         <v>4</v>
@@ -14414,13 +14417,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E38" s="28" t="n">
         <v>27</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G38" s="30" t="n">
         <v>4</v>
@@ -14464,13 +14467,13 @@
         <v>0</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E39" s="28" t="n">
         <v>44</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G39" s="30" t="n">
         <v>4</v>
@@ -14514,13 +14517,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E40" s="28" t="n">
         <v>45</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G40" s="30" t="n">
         <v>4</v>
@@ -14564,13 +14567,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E41" s="28" t="n">
         <v>49</v>
       </c>
       <c r="F41" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G41" s="30" t="n">
         <v>4</v>
@@ -14614,13 +14617,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E42" s="28" t="n">
         <v>56</v>
       </c>
       <c r="F42" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G42" s="30" t="n">
         <v>4</v>
@@ -14664,13 +14667,13 @@
         <v>0</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E43" s="28" t="n">
         <v>66</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G43" s="30" t="n">
         <v>4</v>
@@ -14714,13 +14717,13 @@
         <v>0</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E44" s="28" t="n">
         <v>69</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G44" s="30" t="n">
         <v>4</v>
@@ -14764,13 +14767,13 @@
         <v>0</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45" s="28" t="n">
         <v>98</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G45" s="30" t="n">
         <v>4</v>
@@ -14814,13 +14817,13 @@
         <v>0</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E46" s="28" t="n">
         <v>5</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G46" s="30" t="n">
         <v>2</v>
@@ -14864,13 +14867,13 @@
         <v>0</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E47" s="28" t="n">
         <v>11</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G47" s="30" t="n">
         <v>2</v>
@@ -14914,13 +14917,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E48" s="28" t="n">
         <v>19</v>
       </c>
       <c r="F48" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G48" s="30" t="n">
         <v>2</v>
@@ -14964,13 +14967,13 @@
         <v>0</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E49" s="28" t="n">
         <v>29</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G49" s="30" t="n">
         <v>2</v>
@@ -15014,13 +15017,13 @@
         <v>0</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E50" s="28" t="n">
         <v>41</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G50" s="30" t="n">
         <v>2</v>
@@ -15064,13 +15067,13 @@
         <v>0</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E51" s="28" t="n">
         <v>46</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G51" s="30" t="n">
         <v>2</v>
@@ -15114,13 +15117,13 @@
         <v>0</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E52" s="28" t="n">
         <v>51</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G52" s="30" t="n">
         <v>2</v>
@@ -15164,13 +15167,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E53" s="28" t="n">
         <v>57</v>
       </c>
       <c r="F53" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G53" s="30" t="n">
         <v>2</v>
@@ -15214,13 +15217,13 @@
         <v>0</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E54" s="28" t="n">
         <v>61</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G54" s="30" t="n">
         <v>2</v>
@@ -15264,13 +15267,13 @@
         <v>0</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E55" s="28" t="n">
         <v>63</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G55" s="30" t="n">
         <v>2</v>
@@ -15314,13 +15317,13 @@
         <v>0</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E56" s="28" t="n">
         <v>73</v>
       </c>
       <c r="F56" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G56" s="30" t="n">
         <v>2</v>
@@ -15364,13 +15367,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E57" s="28" t="n">
         <v>75</v>
       </c>
       <c r="F57" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G57" s="30" t="n">
         <v>2</v>
@@ -15414,13 +15417,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E58" s="28" t="n">
         <v>84</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G58" s="30" t="n">
         <v>2</v>
@@ -15464,13 +15467,13 @@
         <v>0</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E59" s="28" t="n">
         <v>92</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G59" s="30" t="n">
         <v>2</v>
@@ -15514,13 +15517,13 @@
         <v>0</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E60" s="28" t="n">
         <v>7</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G60" s="30" t="n">
         <v>1</v>
@@ -15564,13 +15567,13 @@
         <v>0</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E61" s="28" t="n">
         <v>9</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G61" s="30" t="n">
         <v>1</v>
@@ -15614,13 +15617,13 @@
         <v>0</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E62" s="28" t="n">
         <v>13</v>
       </c>
       <c r="F62" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G62" s="30" t="n">
         <v>1</v>
@@ -15664,13 +15667,13 @@
         <v>0</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E63" s="28" t="n">
         <v>16</v>
       </c>
       <c r="F63" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G63" s="30" t="n">
         <v>1</v>
@@ -15714,13 +15717,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E64" s="28" t="n">
         <v>32</v>
       </c>
       <c r="F64" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G64" s="30" t="n">
         <v>1</v>
@@ -15764,13 +15767,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E65" s="28" t="n">
         <v>48</v>
       </c>
       <c r="F65" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G65" s="30" t="n">
         <v>1</v>
@@ -15814,13 +15817,13 @@
         <v>0</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E66" s="28" t="n">
         <v>59</v>
       </c>
       <c r="F66" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G66" s="30" t="n">
         <v>1</v>
@@ -15864,13 +15867,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E67" s="28" t="n">
         <v>79</v>
       </c>
       <c r="F67" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G67" s="30" t="n">
         <v>1</v>
@@ -15914,13 +15917,13 @@
         <v>0</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E68" s="28" t="n">
         <v>82</v>
       </c>
       <c r="F68" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G68" s="30" t="n">
         <v>1</v>
@@ -15964,13 +15967,13 @@
         <v>0</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E69" s="28" t="n">
         <v>91</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G69" s="30" t="n">
         <v>1</v>
@@ -16014,13 +16017,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E70" s="28" t="n">
         <v>99</v>
       </c>
       <c r="F70" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G70" s="30" t="n">
         <v>1</v>
@@ -16064,13 +16067,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E71" s="28" t="n">
         <v>17</v>
       </c>
       <c r="F71" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G71" s="30" t="n">
         <v>4</v>
@@ -16114,13 +16117,13 @@
         <v>0</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E72" s="28" t="n">
         <v>25</v>
       </c>
       <c r="F72" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G72" s="30" t="n">
         <v>4</v>
@@ -16164,13 +16167,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E73" s="28" t="n">
         <v>31</v>
       </c>
       <c r="F73" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G73" s="30" t="n">
         <v>4</v>
@@ -16214,13 +16217,13 @@
         <v>0</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E74" s="28" t="n">
         <v>54</v>
       </c>
       <c r="F74" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G74" s="30" t="n">
         <v>4</v>
@@ -16264,13 +16267,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E75" s="28" t="n">
         <v>71</v>
       </c>
       <c r="F75" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G75" s="30" t="n">
         <v>4</v>
@@ -16314,13 +16317,13 @@
         <v>0</v>
       </c>
       <c r="D76" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E76" s="28" t="n">
         <v>81</v>
       </c>
       <c r="F76" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G76" s="30" t="n">
         <v>4</v>
@@ -16364,13 +16367,13 @@
         <v>0</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E77" s="28" t="n">
         <v>94</v>
       </c>
       <c r="F77" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G77" s="30" t="n">
         <v>4</v>
@@ -16414,13 +16417,13 @@
         <v>0</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E78" s="28" t="n">
         <v>18</v>
       </c>
       <c r="F78" s="29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G78" s="30" t="n">
         <v>2</v>
@@ -16464,13 +16467,13 @@
         <v>0</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E79" s="28" t="n">
         <v>21</v>
       </c>
       <c r="F79" s="29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G79" s="30" t="n">
         <v>2</v>
@@ -16514,13 +16517,13 @@
         <v>0</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E80" s="28" t="n">
         <v>33</v>
       </c>
       <c r="F80" s="29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G80" s="30" t="n">
         <v>2</v>
@@ -16564,13 +16567,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E81" s="28" t="n">
         <v>67</v>
       </c>
       <c r="F81" s="29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G81" s="30" t="n">
         <v>2</v>
@@ -16614,13 +16617,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E82" s="28" t="n">
         <v>68</v>
       </c>
       <c r="F82" s="29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G82" s="30" t="n">
         <v>2</v>
@@ -16664,13 +16667,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E83" s="28" t="n">
         <v>90</v>
       </c>
       <c r="F83" s="29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G83" s="30" t="n">
         <v>2</v>
@@ -16714,13 +16717,13 @@
         <v>0</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E84" s="28" t="n">
         <v>96</v>
       </c>
       <c r="F84" s="29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G84" s="30" t="n">
         <v>2</v>
@@ -16764,13 +16767,13 @@
         <v>0</v>
       </c>
       <c r="D85" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E85" s="28" t="n">
         <v>2</v>
       </c>
       <c r="F85" s="29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G85" s="30" t="n">
         <v>1</v>
@@ -16814,13 +16817,13 @@
         <v>0</v>
       </c>
       <c r="D86" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E86" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F86" s="29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G86" s="30" t="n">
         <v>1</v>
@@ -16864,13 +16867,13 @@
         <v>0</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E87" s="28" t="n">
         <v>34</v>
       </c>
       <c r="F87" s="29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G87" s="30" t="n">
         <v>1</v>
@@ -16914,13 +16917,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E88" s="28" t="n">
         <v>42</v>
       </c>
       <c r="F88" s="29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G88" s="30" t="n">
         <v>1</v>
@@ -16964,13 +16967,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E89" s="28" t="n">
         <v>47</v>
       </c>
       <c r="F89" s="29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G89" s="30" t="n">
         <v>1</v>
@@ -17014,13 +17017,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E90" s="28" t="n">
         <v>62</v>
       </c>
       <c r="F90" s="29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G90" s="30" t="n">
         <v>1</v>
@@ -17064,13 +17067,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E91" s="28" t="n">
         <v>24</v>
       </c>
       <c r="F91" s="29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G91" s="30" t="n">
         <v>4</v>
@@ -17114,13 +17117,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E92" s="28" t="n">
         <v>35</v>
       </c>
       <c r="F92" s="29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G92" s="30" t="n">
         <v>4</v>
@@ -17164,13 +17167,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E93" s="28" t="n">
         <v>52</v>
       </c>
       <c r="F93" s="29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G93" s="30" t="n">
         <v>4</v>
@@ -17214,13 +17217,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E94" s="28" t="n">
         <v>58</v>
       </c>
       <c r="F94" s="29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G94" s="30" t="n">
         <v>4</v>
@@ -17264,13 +17267,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E95" s="28" t="n">
         <v>70</v>
       </c>
       <c r="F95" s="29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G95" s="30" t="n">
         <v>4</v>
@@ -17314,13 +17317,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E96" s="28" t="n">
         <v>76</v>
       </c>
       <c r="F96" s="29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G96" s="30" t="n">
         <v>4</v>
@@ -17364,13 +17367,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E97" s="28" t="n">
         <v>80</v>
       </c>
       <c r="F97" s="29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G97" s="30" t="n">
         <v>4</v>
@@ -17414,13 +17417,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E98" s="28" t="n">
         <v>14</v>
       </c>
       <c r="F98" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G98" s="30" t="n">
         <v>2</v>
@@ -17464,13 +17467,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E99" s="28" t="n">
         <v>20</v>
       </c>
       <c r="F99" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G99" s="30" t="n">
         <v>2</v>
@@ -17514,13 +17517,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E100" s="28" t="n">
         <v>26</v>
       </c>
       <c r="F100" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G100" s="30" t="n">
         <v>2</v>
@@ -17553,13 +17556,13 @@
     </row>
     <row r="101" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D101" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E101" s="28" t="n">
         <v>50</v>
       </c>
       <c r="F101" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G101" s="30" t="n">
         <v>2</v>
@@ -17592,13 +17595,13 @@
     </row>
     <row r="102" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D102" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E102" s="28" t="n">
         <v>78</v>
       </c>
       <c r="F102" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G102" s="30" t="n">
         <v>2</v>
@@ -17631,13 +17634,13 @@
     </row>
     <row r="103" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D103" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E103" s="28" t="n">
         <v>88</v>
       </c>
       <c r="F103" s="29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G103" s="30" t="n">
         <v>2</v>
@@ -17670,13 +17673,13 @@
     </row>
     <row r="104" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E104" s="28" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G104" s="30" t="n">
         <v>3</v>
@@ -17709,13 +17712,13 @@
     </row>
     <row r="105" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E105" s="28" t="n">
         <v>28</v>
       </c>
       <c r="F105" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G105" s="30" t="n">
         <v>3</v>
@@ -17748,13 +17751,13 @@
     </row>
     <row r="106" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D106" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E106" s="28" t="n">
         <v>30</v>
       </c>
       <c r="F106" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G106" s="30" t="n">
         <v>3</v>
@@ -17787,13 +17790,13 @@
     </row>
     <row r="107" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E107" s="28" t="n">
         <v>36</v>
       </c>
       <c r="F107" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G107" s="30" t="n">
         <v>3</v>
@@ -17826,13 +17829,13 @@
     </row>
     <row r="108" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D108" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E108" s="28" t="n">
         <v>40</v>
       </c>
       <c r="F108" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G108" s="30" t="n">
         <v>3</v>
@@ -17865,13 +17868,13 @@
     </row>
     <row r="109" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D109" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E109" s="28" t="n">
         <v>60</v>
       </c>
       <c r="F109" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G109" s="30" t="n">
         <v>3</v>
@@ -17904,13 +17907,13 @@
     </row>
     <row r="110" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D110" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E110" s="28" t="n">
         <v>72</v>
       </c>
       <c r="F110" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G110" s="30" t="n">
         <v>3</v>
@@ -17943,13 +17946,13 @@
     </row>
     <row r="111" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D111" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E111" s="28" t="n">
         <v>83</v>
       </c>
       <c r="F111" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G111" s="30" t="n">
         <v>3</v>
@@ -17982,13 +17985,13 @@
     </row>
     <row r="112" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E112" s="28" t="n">
         <v>85</v>
       </c>
       <c r="F112" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G112" s="30" t="n">
         <v>3</v>
@@ -18021,13 +18024,13 @@
     </row>
     <row r="113" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D113" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E113" s="28" t="n">
         <v>95</v>
       </c>
       <c r="F113" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G113" s="30" t="n">
         <v>3</v>
@@ -18060,13 +18063,13 @@
     </row>
     <row r="114" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D114" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E114" s="28" t="n">
         <v>97</v>
       </c>
       <c r="F114" s="29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G114" s="30" t="n">
         <v>3</v>
@@ -18099,13 +18102,13 @@
     </row>
     <row r="115" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D115" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E115" s="28" t="n">
         <v>4</v>
       </c>
       <c r="F115" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G115" s="30" t="n">
         <v>3</v>
@@ -18138,13 +18141,13 @@
     </row>
     <row r="116" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E116" s="28" t="n">
         <v>8</v>
       </c>
       <c r="F116" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G116" s="30" t="n">
         <v>3</v>
@@ -18177,13 +18180,13 @@
     </row>
     <row r="117" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D117" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E117" s="28" t="n">
         <v>10</v>
       </c>
       <c r="F117" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G117" s="30" t="n">
         <v>3</v>
@@ -18216,13 +18219,13 @@
     </row>
     <row r="118" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D118" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E118" s="28" t="n">
         <v>12</v>
       </c>
       <c r="F118" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G118" s="30" t="n">
         <v>3</v>
@@ -18255,13 +18258,13 @@
     </row>
     <row r="119" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D119" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E119" s="28" t="n">
         <v>22</v>
       </c>
       <c r="F119" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G119" s="30" t="n">
         <v>3</v>
@@ -18294,13 +18297,13 @@
     </row>
     <row r="120" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E120" s="28" t="n">
         <v>38</v>
       </c>
       <c r="F120" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G120" s="30" t="n">
         <v>3</v>
@@ -18333,13 +18336,13 @@
     </row>
     <row r="121" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D121" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E121" s="28" t="n">
         <v>55</v>
       </c>
       <c r="F121" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G121" s="30" t="n">
         <v>3</v>
@@ -18372,13 +18375,13 @@
     </row>
     <row r="122" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D122" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E122" s="28" t="n">
         <v>65</v>
       </c>
       <c r="F122" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G122" s="30" t="n">
         <v>3</v>
@@ -18411,13 +18414,13 @@
     </row>
     <row r="123" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D123" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E123" s="28" t="n">
         <v>74</v>
       </c>
       <c r="F123" s="29" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G123" s="30" t="n">
         <v>3</v>
@@ -18450,13 +18453,13 @@
     </row>
     <row r="124" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D124" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E124" s="28" t="n">
         <v>37</v>
       </c>
       <c r="F124" s="29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G124" s="30" t="n">
         <v>3</v>
@@ -18489,13 +18492,13 @@
     </row>
     <row r="125" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D125" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E125" s="28" t="n">
         <v>39</v>
       </c>
       <c r="F125" s="29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G125" s="30" t="n">
         <v>3</v>
@@ -18528,13 +18531,13 @@
     </row>
     <row r="126" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D126" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E126" s="28" t="n">
         <v>43</v>
       </c>
       <c r="F126" s="29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G126" s="30" t="n">
         <v>3</v>
@@ -18567,13 +18570,13 @@
     </row>
     <row r="127" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E127" s="28" t="n">
         <v>53</v>
       </c>
       <c r="F127" s="29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G127" s="30" t="n">
         <v>3</v>
@@ -18606,13 +18609,13 @@
     </row>
     <row r="128" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E128" s="28" t="n">
         <v>64</v>
       </c>
       <c r="F128" s="29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G128" s="30" t="n">
         <v>3</v>
@@ -18645,13 +18648,13 @@
     </row>
     <row r="129" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D129" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E129" s="28" t="n">
         <v>86</v>
       </c>
       <c r="F129" s="29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G129" s="30" t="n">
         <v>3</v>
@@ -18684,13 +18687,13 @@
     </row>
     <row r="130" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E130" s="28" t="n">
         <v>89</v>
       </c>
       <c r="F130" s="29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G130" s="30" t="n">
         <v>3</v>
@@ -18723,13 +18726,13 @@
     </row>
     <row r="131" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E131" s="28" t="n">
         <v>93</v>
       </c>
       <c r="F131" s="29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G131" s="30" t="n">
         <v>3</v>
@@ -18762,13 +18765,13 @@
     </row>
     <row r="132" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D132" s="28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E132" s="28" t="n">
         <v>100</v>
       </c>
       <c r="F132" s="29" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G132" s="30" t="n">
         <v>3</v>
@@ -18857,7 +18860,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" s="8"/>
       <c r="F1" s="9"/>
@@ -18902,16 +18905,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="15"/>
       <c r="J3" s="16"/>
@@ -18943,7 +18946,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="16"/>
     </row>
@@ -18960,7 +18963,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">(4-D3)*20+1</f>
@@ -18978,7 +18981,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="16"/>
     </row>
@@ -19014,7 +19017,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="16"/>
     </row>
@@ -19031,7 +19034,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">E6+1</f>
@@ -19050,7 +19053,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7" s="16"/>
     </row>
@@ -19087,7 +19090,7 @@
         <v>103</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" s="16"/>
     </row>
@@ -19104,7 +19107,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">E8+1</f>
@@ -19151,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
@@ -19169,7 +19172,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">E10+1</f>
@@ -19235,7 +19238,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">E12+1</f>
@@ -19298,7 +19301,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="18" t="n">
         <f aca="false">E14+1</f>
@@ -19358,7 +19361,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">E16+1</f>
@@ -19424,7 +19427,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="18" t="n">
         <f aca="false">E18+1</f>
@@ -19455,7 +19458,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E20" s="18" t="n">
         <f aca="false">E19+1</f>
@@ -19486,7 +19489,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">E20+1</f>
@@ -19517,7 +19520,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">E21+1</f>
@@ -19548,7 +19551,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" s="18" t="n">
         <f aca="false">E22+1</f>
@@ -19636,7 +19639,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" s="18" t="n">
         <f aca="false">D29</f>
@@ -19667,7 +19670,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E27" s="18" t="n">
         <f aca="false">E26+1</f>
@@ -19698,7 +19701,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">E27+1</f>
@@ -19799,163 +19802,163 @@
         <v>0</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G32" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H32" s="27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J32" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K32" s="27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L32" s="27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M32" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N32" s="27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O32" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P32" s="27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q32" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R32" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S32" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T32" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U32" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V32" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W32" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X32" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y32" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z32" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AA32" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AB32" s="27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AC32" s="27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AD32" s="27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AE32" s="27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AF32" s="27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG32" s="27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH32" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI32" s="27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AJ32" s="27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK32" s="27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AL32" s="27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AM32" s="27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AN32" s="27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AO32" s="27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AP32" s="27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AQ32" s="27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AR32" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AS32" s="27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT32" s="27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AU32" s="27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AV32" s="27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AW32" s="27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AX32" s="27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY32" s="27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AZ32" s="27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BA32" s="27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BB32" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="BC32" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BD32" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19971,13 +19974,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E33" s="28" t="n">
         <v>7</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G33" s="30" t="n">
         <v>1</v>
@@ -20059,13 +20062,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E34" s="28" t="n">
         <v>17</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G34" s="30" t="n">
         <v>1</v>
@@ -20145,13 +20148,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E35" s="28" t="n">
         <v>23</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G35" s="30" t="n">
         <v>1</v>
@@ -20231,13 +20234,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E36" s="28" t="n">
         <v>51</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G36" s="30" t="n">
         <v>1</v>
@@ -20317,13 +20320,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E37" s="28" t="n">
         <v>58</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G37" s="30" t="n">
         <v>1</v>
@@ -20405,13 +20408,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E38" s="28" t="n">
         <v>65</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G38" s="30" t="n">
         <v>1</v>
@@ -20491,13 +20494,13 @@
         <v>0</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E39" s="28" t="n">
         <v>67</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G39" s="30" t="n">
         <v>1</v>
@@ -20577,13 +20580,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E40" s="28" t="n">
         <v>73</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G40" s="30" t="n">
         <v>1</v>
@@ -20665,13 +20668,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E41" s="28" t="n">
         <v>74</v>
       </c>
       <c r="F41" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G41" s="30" t="n">
         <v>1</v>
@@ -20751,13 +20754,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E42" s="28" t="n">
         <v>91</v>
       </c>
       <c r="F42" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G42" s="30" t="n">
         <v>1</v>
@@ -20837,13 +20840,13 @@
         <v>0</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E43" s="28" t="n">
         <v>100</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G43" s="30" t="n">
         <v>1</v>
@@ -20923,13 +20926,13 @@
         <v>0</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E44" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G44" s="30" t="n">
         <v>2</v>
@@ -21009,13 +21012,13 @@
         <v>0</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E45" s="28" t="n">
         <v>13</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G45" s="30" t="n">
         <v>2</v>
@@ -21095,13 +21098,13 @@
         <v>0</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E46" s="28" t="n">
         <v>22</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G46" s="30" t="n">
         <v>2</v>
@@ -21181,13 +21184,13 @@
         <v>0</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E47" s="28" t="n">
         <v>26</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G47" s="30" t="n">
         <v>2</v>
@@ -21267,13 +21270,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E48" s="28" t="n">
         <v>35</v>
       </c>
       <c r="F48" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G48" s="30" t="n">
         <v>2</v>
@@ -21353,13 +21356,13 @@
         <v>0</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E49" s="28" t="n">
         <v>38</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G49" s="30" t="n">
         <v>2</v>
@@ -21439,13 +21442,13 @@
         <v>0</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E50" s="28" t="n">
         <v>45</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G50" s="30" t="n">
         <v>2</v>
@@ -21525,13 +21528,13 @@
         <v>0</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E51" s="28" t="n">
         <v>47</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G51" s="30" t="n">
         <v>2</v>
@@ -21611,13 +21614,13 @@
         <v>0</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E52" s="28" t="n">
         <v>55</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G52" s="30" t="n">
         <v>2</v>
@@ -21697,13 +21700,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E53" s="28" t="n">
         <v>72</v>
       </c>
       <c r="F53" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G53" s="30" t="n">
         <v>2</v>
@@ -21783,13 +21786,13 @@
         <v>0</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E54" s="28" t="n">
         <v>78</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G54" s="30" t="n">
         <v>2</v>
@@ -21869,13 +21872,13 @@
         <v>0</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E55" s="28" t="n">
         <v>88</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G55" s="30" t="n">
         <v>2</v>
@@ -21955,13 +21958,13 @@
         <v>0</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E56" s="28" t="n">
         <v>89</v>
       </c>
       <c r="F56" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G56" s="30" t="n">
         <v>2</v>
@@ -22041,13 +22044,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E57" s="28" t="n">
         <v>97</v>
       </c>
       <c r="F57" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G57" s="30" t="n">
         <v>2</v>
@@ -22127,13 +22130,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E58" s="28" t="n">
         <v>5</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G58" s="30" t="n">
         <v>3</v>
@@ -22213,13 +22216,13 @@
         <v>0</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E59" s="28" t="n">
         <v>12</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G59" s="30" t="n">
         <v>3</v>
@@ -22299,13 +22302,13 @@
         <v>0</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E60" s="28" t="n">
         <v>14</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G60" s="30" t="n">
         <v>3</v>
@@ -22385,13 +22388,13 @@
         <v>0</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E61" s="28" t="n">
         <v>39</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G61" s="30" t="n">
         <v>3</v>
@@ -22471,13 +22474,13 @@
         <v>0</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E62" s="28" t="n">
         <v>49</v>
       </c>
       <c r="F62" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G62" s="30" t="n">
         <v>3</v>
@@ -22557,13 +22560,13 @@
         <v>0</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E63" s="28" t="n">
         <v>62</v>
       </c>
       <c r="F63" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G63" s="30" t="n">
         <v>3</v>
@@ -22643,13 +22646,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E64" s="28" t="n">
         <v>79</v>
       </c>
       <c r="F64" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G64" s="30" t="n">
         <v>3</v>
@@ -22729,13 +22732,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E65" s="28" t="n">
         <v>98</v>
       </c>
       <c r="F65" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G65" s="30" t="n">
         <v>3</v>
@@ -22815,13 +22818,13 @@
         <v>0</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E66" s="28" t="n">
         <v>8</v>
       </c>
       <c r="F66" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G66" s="30" t="n">
         <v>1</v>
@@ -22901,13 +22904,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E67" s="28" t="n">
         <v>9</v>
       </c>
       <c r="F67" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G67" s="30" t="n">
         <v>1</v>
@@ -22987,13 +22990,13 @@
         <v>0</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E68" s="28" t="n">
         <v>24</v>
       </c>
       <c r="F68" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G68" s="30" t="n">
         <v>1</v>
@@ -23073,13 +23076,13 @@
         <v>0</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E69" s="28" t="n">
         <v>30</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G69" s="30" t="n">
         <v>1</v>
@@ -23159,13 +23162,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E70" s="28" t="n">
         <v>32</v>
       </c>
       <c r="F70" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G70" s="30" t="n">
         <v>1</v>
@@ -23245,13 +23248,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E71" s="28" t="n">
         <v>36</v>
       </c>
       <c r="F71" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G71" s="30" t="n">
         <v>1</v>
@@ -23331,13 +23334,13 @@
         <v>0</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E72" s="28" t="n">
         <v>53</v>
       </c>
       <c r="F72" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G72" s="30" t="n">
         <v>1</v>
@@ -23417,13 +23420,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E73" s="28" t="n">
         <v>61</v>
       </c>
       <c r="F73" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G73" s="30" t="n">
         <v>1</v>
@@ -23503,13 +23506,13 @@
         <v>0</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E74" s="28" t="n">
         <v>70</v>
       </c>
       <c r="F74" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G74" s="30" t="n">
         <v>1</v>
@@ -23589,13 +23592,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E75" s="28" t="n">
         <v>4</v>
       </c>
       <c r="F75" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G75" s="30" t="n">
         <v>2</v>
@@ -23675,13 +23678,13 @@
         <v>0</v>
       </c>
       <c r="D76" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E76" s="28" t="n">
         <v>6</v>
       </c>
       <c r="F76" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G76" s="30" t="n">
         <v>2</v>
@@ -23761,13 +23764,13 @@
         <v>0</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E77" s="28" t="n">
         <v>19</v>
       </c>
       <c r="F77" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G77" s="30" t="n">
         <v>2</v>
@@ -23847,13 +23850,13 @@
         <v>0</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E78" s="28" t="n">
         <v>25</v>
       </c>
       <c r="F78" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G78" s="30" t="n">
         <v>2</v>
@@ -23933,13 +23936,13 @@
         <v>0</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E79" s="28" t="n">
         <v>28</v>
       </c>
       <c r="F79" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G79" s="30" t="n">
         <v>2</v>
@@ -24019,13 +24022,13 @@
         <v>0</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E80" s="28" t="n">
         <v>34</v>
       </c>
       <c r="F80" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G80" s="30" t="n">
         <v>2</v>
@@ -24105,13 +24108,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E81" s="28" t="n">
         <v>44</v>
       </c>
       <c r="F81" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G81" s="30" t="n">
         <v>2</v>
@@ -24191,13 +24194,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E82" s="28" t="n">
         <v>52</v>
       </c>
       <c r="F82" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G82" s="30" t="n">
         <v>2</v>
@@ -24277,13 +24280,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E83" s="28" t="n">
         <v>54</v>
       </c>
       <c r="F83" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G83" s="30" t="n">
         <v>2</v>
@@ -24363,13 +24366,13 @@
         <v>0</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E84" s="28" t="n">
         <v>56</v>
       </c>
       <c r="F84" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G84" s="30" t="n">
         <v>2</v>
@@ -24449,13 +24452,13 @@
         <v>0</v>
       </c>
       <c r="D85" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E85" s="28" t="n">
         <v>57</v>
       </c>
       <c r="F85" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G85" s="30" t="n">
         <v>2</v>
@@ -24535,13 +24538,13 @@
         <v>0</v>
       </c>
       <c r="D86" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E86" s="28" t="n">
         <v>66</v>
       </c>
       <c r="F86" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G86" s="30" t="n">
         <v>2</v>
@@ -24621,13 +24624,13 @@
         <v>0</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E87" s="28" t="n">
         <v>71</v>
       </c>
       <c r="F87" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G87" s="30" t="n">
         <v>2</v>
@@ -24707,13 +24710,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E88" s="28" t="n">
         <v>77</v>
       </c>
       <c r="F88" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G88" s="30" t="n">
         <v>2</v>
@@ -24793,13 +24796,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E89" s="28" t="n">
         <v>83</v>
       </c>
       <c r="F89" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G89" s="30" t="n">
         <v>2</v>
@@ -24879,13 +24882,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E90" s="28" t="n">
         <v>85</v>
       </c>
       <c r="F90" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G90" s="30" t="n">
         <v>2</v>
@@ -24965,13 +24968,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E91" s="28" t="n">
         <v>90</v>
       </c>
       <c r="F91" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G91" s="30" t="n">
         <v>2</v>
@@ -25051,13 +25054,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E92" s="28" t="n">
         <v>94</v>
       </c>
       <c r="F92" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G92" s="30" t="n">
         <v>2</v>
@@ -25137,13 +25140,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E93" s="28" t="n">
         <v>96</v>
       </c>
       <c r="F93" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G93" s="30" t="n">
         <v>2</v>
@@ -25223,13 +25226,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E94" s="28" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G94" s="30" t="n">
         <v>3</v>
@@ -25309,13 +25312,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E95" s="28" t="n">
         <v>15</v>
       </c>
       <c r="F95" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G95" s="30" t="n">
         <v>3</v>
@@ -25395,13 +25398,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E96" s="28" t="n">
         <v>21</v>
       </c>
       <c r="F96" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G96" s="30" t="n">
         <v>3</v>
@@ -25481,13 +25484,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E97" s="28" t="n">
         <v>27</v>
       </c>
       <c r="F97" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G97" s="30" t="n">
         <v>3</v>
@@ -25567,13 +25570,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E98" s="28" t="n">
         <v>37</v>
       </c>
       <c r="F98" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G98" s="30" t="n">
         <v>3</v>
@@ -25653,13 +25656,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E99" s="28" t="n">
         <v>40</v>
       </c>
       <c r="F99" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G99" s="30" t="n">
         <v>3</v>
@@ -25739,13 +25742,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E100" s="28" t="n">
         <v>63</v>
       </c>
       <c r="F100" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G100" s="30" t="n">
         <v>3</v>
@@ -25814,13 +25817,13 @@
     </row>
     <row r="101" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D101" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E101" s="28" t="n">
         <v>69</v>
       </c>
       <c r="F101" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G101" s="30" t="n">
         <v>3</v>
@@ -25889,13 +25892,13 @@
     </row>
     <row r="102" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D102" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E102" s="28" t="n">
         <v>76</v>
       </c>
       <c r="F102" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G102" s="30" t="n">
         <v>3</v>
@@ -25964,13 +25967,13 @@
     </row>
     <row r="103" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D103" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E103" s="28" t="n">
         <v>99</v>
       </c>
       <c r="F103" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G103" s="30" t="n">
         <v>3</v>
@@ -26039,13 +26042,13 @@
     </row>
     <row r="104" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E104" s="28" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G104" s="30" t="n">
         <v>1</v>
@@ -26114,13 +26117,13 @@
     </row>
     <row r="105" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E105" s="28" t="n">
         <v>10</v>
       </c>
       <c r="F105" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G105" s="30" t="n">
         <v>1</v>
@@ -26189,13 +26192,13 @@
     </row>
     <row r="106" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D106" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E106" s="28" t="n">
         <v>16</v>
       </c>
       <c r="F106" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G106" s="30" t="n">
         <v>1</v>
@@ -26264,13 +26267,13 @@
     </row>
     <row r="107" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E107" s="28" t="n">
         <v>33</v>
       </c>
       <c r="F107" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G107" s="30" t="n">
         <v>1</v>
@@ -26339,13 +26342,13 @@
     </row>
     <row r="108" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D108" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E108" s="28" t="n">
         <v>41</v>
       </c>
       <c r="F108" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G108" s="30" t="n">
         <v>1</v>
@@ -26414,13 +26417,13 @@
     </row>
     <row r="109" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D109" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E109" s="28" t="n">
         <v>42</v>
       </c>
       <c r="F109" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G109" s="30" t="n">
         <v>1</v>
@@ -26489,13 +26492,13 @@
     </row>
     <row r="110" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D110" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E110" s="28" t="n">
         <v>68</v>
       </c>
       <c r="F110" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G110" s="30" t="n">
         <v>1</v>
@@ -26564,13 +26567,13 @@
     </row>
     <row r="111" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D111" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E111" s="28" t="n">
         <v>75</v>
       </c>
       <c r="F111" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G111" s="30" t="n">
         <v>1</v>
@@ -26639,13 +26642,13 @@
     </row>
     <row r="112" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E112" s="28" t="n">
         <v>82</v>
       </c>
       <c r="F112" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G112" s="30" t="n">
         <v>1</v>
@@ -26714,13 +26717,13 @@
     </row>
     <row r="113" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D113" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E113" s="28" t="n">
         <v>86</v>
       </c>
       <c r="F113" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G113" s="30" t="n">
         <v>1</v>
@@ -26789,13 +26792,13 @@
     </row>
     <row r="114" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D114" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E114" s="28" t="n">
         <v>93</v>
       </c>
       <c r="F114" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G114" s="30" t="n">
         <v>1</v>
@@ -26864,13 +26867,13 @@
     </row>
     <row r="115" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D115" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E115" s="28" t="n">
         <v>11</v>
       </c>
       <c r="F115" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G115" s="30" t="n">
         <v>2</v>
@@ -26939,13 +26942,13 @@
     </row>
     <row r="116" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E116" s="28" t="n">
         <v>20</v>
       </c>
       <c r="F116" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G116" s="30" t="n">
         <v>2</v>
@@ -27014,13 +27017,13 @@
     </row>
     <row r="117" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D117" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E117" s="28" t="n">
         <v>29</v>
       </c>
       <c r="F117" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G117" s="30" t="n">
         <v>2</v>
@@ -27089,13 +27092,13 @@
     </row>
     <row r="118" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D118" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E118" s="28" t="n">
         <v>46</v>
       </c>
       <c r="F118" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G118" s="30" t="n">
         <v>2</v>
@@ -27164,13 +27167,13 @@
     </row>
     <row r="119" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D119" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E119" s="28" t="n">
         <v>50</v>
       </c>
       <c r="F119" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G119" s="30" t="n">
         <v>2</v>
@@ -27239,13 +27242,13 @@
     </row>
     <row r="120" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E120" s="28" t="n">
         <v>81</v>
       </c>
       <c r="F120" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G120" s="30" t="n">
         <v>2</v>
@@ -27314,13 +27317,13 @@
     </row>
     <row r="121" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D121" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E121" s="28" t="n">
         <v>84</v>
       </c>
       <c r="F121" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G121" s="30" t="n">
         <v>2</v>
@@ -27389,13 +27392,13 @@
     </row>
     <row r="122" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D122" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E122" s="28" t="n">
         <v>87</v>
       </c>
       <c r="F122" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G122" s="30" t="n">
         <v>2</v>
@@ -27464,13 +27467,13 @@
     </row>
     <row r="123" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D123" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E123" s="28" t="n">
         <v>18</v>
       </c>
       <c r="F123" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G123" s="30" t="n">
         <v>3</v>
@@ -27539,13 +27542,13 @@
     </row>
     <row r="124" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D124" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E124" s="28" t="n">
         <v>31</v>
       </c>
       <c r="F124" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G124" s="30" t="n">
         <v>3</v>
@@ -27614,13 +27617,13 @@
     </row>
     <row r="125" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D125" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E125" s="28" t="n">
         <v>43</v>
       </c>
       <c r="F125" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G125" s="30" t="n">
         <v>3</v>
@@ -27689,13 +27692,13 @@
     </row>
     <row r="126" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D126" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E126" s="28" t="n">
         <v>48</v>
       </c>
       <c r="F126" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G126" s="30" t="n">
         <v>3</v>
@@ -27764,13 +27767,13 @@
     </row>
     <row r="127" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E127" s="28" t="n">
         <v>59</v>
       </c>
       <c r="F127" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G127" s="30" t="n">
         <v>3</v>
@@ -27839,13 +27842,13 @@
     </row>
     <row r="128" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E128" s="28" t="n">
         <v>60</v>
       </c>
       <c r="F128" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G128" s="30" t="n">
         <v>3</v>
@@ -27914,13 +27917,13 @@
     </row>
     <row r="129" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D129" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E129" s="28" t="n">
         <v>64</v>
       </c>
       <c r="F129" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G129" s="30" t="n">
         <v>3</v>
@@ -27989,13 +27992,13 @@
     </row>
     <row r="130" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E130" s="28" t="n">
         <v>80</v>
       </c>
       <c r="F130" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G130" s="30" t="n">
         <v>3</v>
@@ -28064,13 +28067,13 @@
     </row>
     <row r="131" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E131" s="28" t="n">
         <v>92</v>
       </c>
       <c r="F131" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G131" s="30" t="n">
         <v>3</v>
@@ -28139,13 +28142,13 @@
     </row>
     <row r="132" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D132" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E132" s="28" t="n">
         <v>95</v>
       </c>
       <c r="F132" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G132" s="30" t="n">
         <v>3</v>
@@ -28214,7 +28217,7 @@
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D133" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E133" s="6" t="n">
         <v>1</v>
@@ -28228,13 +28231,13 @@
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D134" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E134" s="6" t="n">
         <v>9999999</v>
       </c>
       <c r="F134" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -28294,7 +28297,7 @@
         <v>31</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E1" s="8"/>
       <c r="F1" s="9"/>
@@ -28339,16 +28342,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="15"/>
       <c r="J3" s="16"/>
@@ -28380,7 +28383,7 @@
         <v>100</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J4" s="16"/>
     </row>
@@ -28397,7 +28400,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="18" t="n">
         <f aca="false">(4-D3)*20+1</f>
@@ -28415,7 +28418,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="16"/>
     </row>
@@ -28451,7 +28454,7 @@
         <v>100</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="16"/>
     </row>
@@ -28468,7 +28471,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="18" t="n">
         <f aca="false">E6+1</f>
@@ -28487,7 +28490,7 @@
         <v>100</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7" s="16"/>
     </row>
@@ -28524,7 +28527,7 @@
         <v>103</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J8" s="16"/>
     </row>
@@ -28541,7 +28544,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="18" t="n">
         <f aca="false">E8+1</f>
@@ -28588,7 +28591,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I10" s="16"/>
       <c r="J10" s="16"/>
@@ -28606,7 +28609,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="18" t="n">
         <f aca="false">E10+1</f>
@@ -28672,7 +28675,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="18" t="n">
         <f aca="false">E12+1</f>
@@ -28735,7 +28738,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" s="18" t="n">
         <f aca="false">E14+1</f>
@@ -28795,7 +28798,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="18" t="n">
         <f aca="false">E16+1</f>
@@ -28861,7 +28864,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E19" s="18" t="n">
         <f aca="false">E18+1</f>
@@ -28892,7 +28895,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E20" s="18" t="n">
         <f aca="false">E19+1</f>
@@ -28923,7 +28926,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18" t="n">
         <f aca="false">E20+1</f>
@@ -28954,7 +28957,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">E21+1</f>
@@ -28985,7 +28988,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" s="18" t="n">
         <f aca="false">E22+1</f>
@@ -29073,7 +29076,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E26" s="18" t="n">
         <f aca="false">D29</f>
@@ -29104,7 +29107,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E27" s="18" t="n">
         <f aca="false">E26+1</f>
@@ -29135,7 +29138,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E28" s="18" t="n">
         <f aca="false">E27+1</f>
@@ -29236,163 +29239,163 @@
         <v>0</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G32" s="27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H32" s="27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I32" s="27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J32" s="27" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K32" s="27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L32" s="27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M32" s="27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N32" s="27" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O32" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P32" s="27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q32" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R32" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S32" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T32" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U32" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V32" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W32" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X32" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y32" s="27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Z32" s="27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AA32" s="27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AB32" s="27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AC32" s="27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AD32" s="27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AE32" s="27" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AF32" s="27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG32" s="27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH32" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI32" s="27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AJ32" s="27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AK32" s="27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AL32" s="27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AM32" s="27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AN32" s="27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AO32" s="27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AP32" s="27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AQ32" s="27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AR32" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AS32" s="27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AT32" s="27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AU32" s="27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AV32" s="27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AW32" s="27" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AX32" s="27" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY32" s="27" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AZ32" s="27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BA32" s="27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BB32" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="BC32" s="27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="BD32" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -29408,13 +29411,13 @@
         <v>0</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E33" s="28" t="n">
         <v>7</v>
       </c>
       <c r="F33" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G33" s="30" t="n">
         <v>1</v>
@@ -29496,13 +29499,13 @@
         <v>0</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E34" s="28" t="n">
         <v>17</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G34" s="30" t="n">
         <v>1</v>
@@ -29582,13 +29585,13 @@
         <v>0</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E35" s="28" t="n">
         <v>23</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G35" s="30" t="n">
         <v>1</v>
@@ -29668,13 +29671,13 @@
         <v>0</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E36" s="28" t="n">
         <v>51</v>
       </c>
       <c r="F36" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G36" s="30" t="n">
         <v>1</v>
@@ -29754,13 +29757,13 @@
         <v>0</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E37" s="28" t="n">
         <v>58</v>
       </c>
       <c r="F37" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G37" s="30" t="n">
         <v>1</v>
@@ -29842,13 +29845,13 @@
         <v>0</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E38" s="28" t="n">
         <v>65</v>
       </c>
       <c r="F38" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G38" s="30" t="n">
         <v>1</v>
@@ -29928,13 +29931,13 @@
         <v>0</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E39" s="28" t="n">
         <v>67</v>
       </c>
       <c r="F39" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G39" s="30" t="n">
         <v>1</v>
@@ -30014,13 +30017,13 @@
         <v>0</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E40" s="28" t="n">
         <v>73</v>
       </c>
       <c r="F40" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G40" s="30" t="n">
         <v>1</v>
@@ -30102,13 +30105,13 @@
         <v>0</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E41" s="28" t="n">
         <v>74</v>
       </c>
       <c r="F41" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G41" s="30" t="n">
         <v>1</v>
@@ -30188,13 +30191,13 @@
         <v>0</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E42" s="28" t="n">
         <v>91</v>
       </c>
       <c r="F42" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G42" s="30" t="n">
         <v>1</v>
@@ -30274,13 +30277,13 @@
         <v>0</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E43" s="28" t="n">
         <v>100</v>
       </c>
       <c r="F43" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G43" s="30" t="n">
         <v>1</v>
@@ -30360,13 +30363,13 @@
         <v>0</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E44" s="28" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G44" s="30" t="n">
         <v>2</v>
@@ -30446,13 +30449,13 @@
         <v>0</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E45" s="28" t="n">
         <v>13</v>
       </c>
       <c r="F45" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G45" s="30" t="n">
         <v>2</v>
@@ -30532,13 +30535,13 @@
         <v>0</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E46" s="28" t="n">
         <v>22</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G46" s="30" t="n">
         <v>2</v>
@@ -30618,13 +30621,13 @@
         <v>0</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E47" s="28" t="n">
         <v>26</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G47" s="30" t="n">
         <v>2</v>
@@ -30704,13 +30707,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E48" s="28" t="n">
         <v>35</v>
       </c>
       <c r="F48" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G48" s="30" t="n">
         <v>2</v>
@@ -30790,13 +30793,13 @@
         <v>0</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E49" s="28" t="n">
         <v>38</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G49" s="30" t="n">
         <v>2</v>
@@ -30876,13 +30879,13 @@
         <v>0</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E50" s="28" t="n">
         <v>45</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G50" s="30" t="n">
         <v>2</v>
@@ -30962,13 +30965,13 @@
         <v>0</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E51" s="28" t="n">
         <v>47</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G51" s="30" t="n">
         <v>2</v>
@@ -31048,13 +31051,13 @@
         <v>0</v>
       </c>
       <c r="D52" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E52" s="28" t="n">
         <v>55</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G52" s="30" t="n">
         <v>2</v>
@@ -31134,13 +31137,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E53" s="28" t="n">
         <v>72</v>
       </c>
       <c r="F53" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G53" s="30" t="n">
         <v>2</v>
@@ -31220,13 +31223,13 @@
         <v>0</v>
       </c>
       <c r="D54" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E54" s="28" t="n">
         <v>78</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G54" s="30" t="n">
         <v>2</v>
@@ -31306,13 +31309,13 @@
         <v>0</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E55" s="28" t="n">
         <v>88</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G55" s="30" t="n">
         <v>2</v>
@@ -31392,13 +31395,13 @@
         <v>0</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E56" s="28" t="n">
         <v>89</v>
       </c>
       <c r="F56" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G56" s="30" t="n">
         <v>2</v>
@@ -31478,13 +31481,13 @@
         <v>0</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E57" s="28" t="n">
         <v>97</v>
       </c>
       <c r="F57" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G57" s="30" t="n">
         <v>2</v>
@@ -31564,13 +31567,13 @@
         <v>0</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E58" s="28" t="n">
         <v>5</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G58" s="30" t="n">
         <v>3</v>
@@ -31650,13 +31653,13 @@
         <v>0</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E59" s="28" t="n">
         <v>12</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G59" s="30" t="n">
         <v>3</v>
@@ -31736,13 +31739,13 @@
         <v>0</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E60" s="28" t="n">
         <v>14</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G60" s="30" t="n">
         <v>3</v>
@@ -31822,13 +31825,13 @@
         <v>0</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E61" s="28" t="n">
         <v>39</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G61" s="30" t="n">
         <v>3</v>
@@ -31908,13 +31911,13 @@
         <v>0</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E62" s="28" t="n">
         <v>49</v>
       </c>
       <c r="F62" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G62" s="30" t="n">
         <v>3</v>
@@ -31994,13 +31997,13 @@
         <v>0</v>
       </c>
       <c r="D63" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E63" s="28" t="n">
         <v>62</v>
       </c>
       <c r="F63" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G63" s="30" t="n">
         <v>3</v>
@@ -32080,13 +32083,13 @@
         <v>0</v>
       </c>
       <c r="D64" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E64" s="28" t="n">
         <v>79</v>
       </c>
       <c r="F64" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G64" s="30" t="n">
         <v>3</v>
@@ -32166,13 +32169,13 @@
         <v>0</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E65" s="28" t="n">
         <v>98</v>
       </c>
       <c r="F65" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G65" s="30" t="n">
         <v>3</v>
@@ -32252,13 +32255,13 @@
         <v>0</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E66" s="28" t="n">
         <v>8</v>
       </c>
       <c r="F66" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G66" s="30" t="n">
         <v>1</v>
@@ -32338,13 +32341,13 @@
         <v>0</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E67" s="28" t="n">
         <v>9</v>
       </c>
       <c r="F67" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G67" s="30" t="n">
         <v>1</v>
@@ -32424,13 +32427,13 @@
         <v>0</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E68" s="28" t="n">
         <v>24</v>
       </c>
       <c r="F68" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G68" s="30" t="n">
         <v>1</v>
@@ -32510,13 +32513,13 @@
         <v>0</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E69" s="28" t="n">
         <v>30</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G69" s="30" t="n">
         <v>1</v>
@@ -32596,13 +32599,13 @@
         <v>0</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E70" s="28" t="n">
         <v>32</v>
       </c>
       <c r="F70" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G70" s="30" t="n">
         <v>1</v>
@@ -32682,13 +32685,13 @@
         <v>0</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E71" s="28" t="n">
         <v>36</v>
       </c>
       <c r="F71" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G71" s="30" t="n">
         <v>1</v>
@@ -32768,13 +32771,13 @@
         <v>0</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E72" s="28" t="n">
         <v>53</v>
       </c>
       <c r="F72" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G72" s="30" t="n">
         <v>1</v>
@@ -32854,13 +32857,13 @@
         <v>0</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E73" s="28" t="n">
         <v>61</v>
       </c>
       <c r="F73" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G73" s="30" t="n">
         <v>1</v>
@@ -32940,13 +32943,13 @@
         <v>0</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E74" s="28" t="n">
         <v>70</v>
       </c>
       <c r="F74" s="29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G74" s="30" t="n">
         <v>1</v>
@@ -33026,13 +33029,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E75" s="28" t="n">
         <v>4</v>
       </c>
       <c r="F75" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G75" s="30" t="n">
         <v>2</v>
@@ -33112,13 +33115,13 @@
         <v>0</v>
       </c>
       <c r="D76" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E76" s="28" t="n">
         <v>6</v>
       </c>
       <c r="F76" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G76" s="30" t="n">
         <v>2</v>
@@ -33198,13 +33201,13 @@
         <v>0</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E77" s="28" t="n">
         <v>19</v>
       </c>
       <c r="F77" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G77" s="30" t="n">
         <v>2</v>
@@ -33284,13 +33287,13 @@
         <v>0</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E78" s="28" t="n">
         <v>25</v>
       </c>
       <c r="F78" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G78" s="30" t="n">
         <v>2</v>
@@ -33370,13 +33373,13 @@
         <v>0</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E79" s="28" t="n">
         <v>28</v>
       </c>
       <c r="F79" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G79" s="30" t="n">
         <v>2</v>
@@ -33456,13 +33459,13 @@
         <v>0</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E80" s="28" t="n">
         <v>34</v>
       </c>
       <c r="F80" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G80" s="30" t="n">
         <v>2</v>
@@ -33542,13 +33545,13 @@
         <v>0</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E81" s="28" t="n">
         <v>44</v>
       </c>
       <c r="F81" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G81" s="30" t="n">
         <v>2</v>
@@ -33628,13 +33631,13 @@
         <v>0</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E82" s="28" t="n">
         <v>52</v>
       </c>
       <c r="F82" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G82" s="30" t="n">
         <v>2</v>
@@ -33714,13 +33717,13 @@
         <v>0</v>
       </c>
       <c r="D83" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E83" s="28" t="n">
         <v>54</v>
       </c>
       <c r="F83" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G83" s="30" t="n">
         <v>2</v>
@@ -33800,13 +33803,13 @@
         <v>0</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E84" s="28" t="n">
         <v>56</v>
       </c>
       <c r="F84" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G84" s="30" t="n">
         <v>2</v>
@@ -33886,13 +33889,13 @@
         <v>0</v>
       </c>
       <c r="D85" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E85" s="28" t="n">
         <v>57</v>
       </c>
       <c r="F85" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G85" s="30" t="n">
         <v>2</v>
@@ -33972,13 +33975,13 @@
         <v>0</v>
       </c>
       <c r="D86" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E86" s="28" t="n">
         <v>66</v>
       </c>
       <c r="F86" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G86" s="30" t="n">
         <v>2</v>
@@ -34058,13 +34061,13 @@
         <v>0</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E87" s="28" t="n">
         <v>71</v>
       </c>
       <c r="F87" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G87" s="30" t="n">
         <v>2</v>
@@ -34144,13 +34147,13 @@
         <v>0</v>
       </c>
       <c r="D88" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E88" s="28" t="n">
         <v>77</v>
       </c>
       <c r="F88" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G88" s="30" t="n">
         <v>2</v>
@@ -34230,13 +34233,13 @@
         <v>0</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E89" s="28" t="n">
         <v>83</v>
       </c>
       <c r="F89" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G89" s="30" t="n">
         <v>2</v>
@@ -34316,13 +34319,13 @@
         <v>0</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E90" s="28" t="n">
         <v>85</v>
       </c>
       <c r="F90" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G90" s="30" t="n">
         <v>2</v>
@@ -34402,13 +34405,13 @@
         <v>0</v>
       </c>
       <c r="D91" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E91" s="28" t="n">
         <v>90</v>
       </c>
       <c r="F91" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G91" s="30" t="n">
         <v>2</v>
@@ -34488,13 +34491,13 @@
         <v>0</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E92" s="28" t="n">
         <v>94</v>
       </c>
       <c r="F92" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G92" s="30" t="n">
         <v>2</v>
@@ -34574,13 +34577,13 @@
         <v>0</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E93" s="28" t="n">
         <v>96</v>
       </c>
       <c r="F93" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G93" s="30" t="n">
         <v>2</v>
@@ -34660,13 +34663,13 @@
         <v>0</v>
       </c>
       <c r="D94" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E94" s="28" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G94" s="30" t="n">
         <v>3</v>
@@ -34746,13 +34749,13 @@
         <v>0</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E95" s="28" t="n">
         <v>15</v>
       </c>
       <c r="F95" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G95" s="30" t="n">
         <v>3</v>
@@ -34832,13 +34835,13 @@
         <v>0</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E96" s="28" t="n">
         <v>21</v>
       </c>
       <c r="F96" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G96" s="30" t="n">
         <v>3</v>
@@ -34918,13 +34921,13 @@
         <v>0</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E97" s="28" t="n">
         <v>27</v>
       </c>
       <c r="F97" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G97" s="30" t="n">
         <v>3</v>
@@ -35004,13 +35007,13 @@
         <v>0</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E98" s="28" t="n">
         <v>37</v>
       </c>
       <c r="F98" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G98" s="30" t="n">
         <v>3</v>
@@ -35090,13 +35093,13 @@
         <v>0</v>
       </c>
       <c r="D99" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E99" s="28" t="n">
         <v>40</v>
       </c>
       <c r="F99" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G99" s="30" t="n">
         <v>3</v>
@@ -35176,13 +35179,13 @@
         <v>0</v>
       </c>
       <c r="D100" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E100" s="28" t="n">
         <v>63</v>
       </c>
       <c r="F100" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G100" s="30" t="n">
         <v>3</v>
@@ -35251,13 +35254,13 @@
     </row>
     <row r="101" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D101" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E101" s="28" t="n">
         <v>69</v>
       </c>
       <c r="F101" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G101" s="30" t="n">
         <v>3</v>
@@ -35326,13 +35329,13 @@
     </row>
     <row r="102" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D102" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E102" s="28" t="n">
         <v>76</v>
       </c>
       <c r="F102" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G102" s="30" t="n">
         <v>3</v>
@@ -35401,13 +35404,13 @@
     </row>
     <row r="103" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D103" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E103" s="28" t="n">
         <v>99</v>
       </c>
       <c r="F103" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G103" s="30" t="n">
         <v>3</v>
@@ -35476,13 +35479,13 @@
     </row>
     <row r="104" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D104" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E104" s="28" t="n">
         <v>1</v>
       </c>
       <c r="F104" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G104" s="30" t="n">
         <v>1</v>
@@ -35551,13 +35554,13 @@
     </row>
     <row r="105" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D105" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E105" s="28" t="n">
         <v>10</v>
       </c>
       <c r="F105" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G105" s="30" t="n">
         <v>1</v>
@@ -35626,13 +35629,13 @@
     </row>
     <row r="106" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D106" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E106" s="28" t="n">
         <v>16</v>
       </c>
       <c r="F106" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G106" s="30" t="n">
         <v>1</v>
@@ -35701,13 +35704,13 @@
     </row>
     <row r="107" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D107" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E107" s="28" t="n">
         <v>33</v>
       </c>
       <c r="F107" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G107" s="30" t="n">
         <v>1</v>
@@ -35776,13 +35779,13 @@
     </row>
     <row r="108" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D108" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E108" s="28" t="n">
         <v>41</v>
       </c>
       <c r="F108" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G108" s="30" t="n">
         <v>1</v>
@@ -35851,13 +35854,13 @@
     </row>
     <row r="109" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D109" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E109" s="28" t="n">
         <v>42</v>
       </c>
       <c r="F109" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G109" s="30" t="n">
         <v>1</v>
@@ -35926,13 +35929,13 @@
     </row>
     <row r="110" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D110" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E110" s="28" t="n">
         <v>68</v>
       </c>
       <c r="F110" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G110" s="30" t="n">
         <v>1</v>
@@ -36001,13 +36004,13 @@
     </row>
     <row r="111" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D111" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E111" s="28" t="n">
         <v>75</v>
       </c>
       <c r="F111" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G111" s="30" t="n">
         <v>1</v>
@@ -36076,13 +36079,13 @@
     </row>
     <row r="112" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D112" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E112" s="28" t="n">
         <v>82</v>
       </c>
       <c r="F112" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G112" s="30" t="n">
         <v>1</v>
@@ -36151,13 +36154,13 @@
     </row>
     <row r="113" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D113" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E113" s="28" t="n">
         <v>86</v>
       </c>
       <c r="F113" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G113" s="30" t="n">
         <v>1</v>
@@ -36226,13 +36229,13 @@
     </row>
     <row r="114" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D114" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E114" s="28" t="n">
         <v>93</v>
       </c>
       <c r="F114" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G114" s="30" t="n">
         <v>1</v>
@@ -36301,13 +36304,13 @@
     </row>
     <row r="115" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D115" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E115" s="28" t="n">
         <v>11</v>
       </c>
       <c r="F115" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G115" s="30" t="n">
         <v>2</v>
@@ -36376,13 +36379,13 @@
     </row>
     <row r="116" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D116" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E116" s="28" t="n">
         <v>20</v>
       </c>
       <c r="F116" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G116" s="30" t="n">
         <v>2</v>
@@ -36451,13 +36454,13 @@
     </row>
     <row r="117" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D117" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E117" s="28" t="n">
         <v>29</v>
       </c>
       <c r="F117" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G117" s="30" t="n">
         <v>2</v>
@@ -36526,13 +36529,13 @@
     </row>
     <row r="118" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D118" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E118" s="28" t="n">
         <v>46</v>
       </c>
       <c r="F118" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G118" s="30" t="n">
         <v>2</v>
@@ -36601,13 +36604,13 @@
     </row>
     <row r="119" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D119" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E119" s="28" t="n">
         <v>50</v>
       </c>
       <c r="F119" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G119" s="30" t="n">
         <v>2</v>
@@ -36676,13 +36679,13 @@
     </row>
     <row r="120" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D120" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E120" s="28" t="n">
         <v>81</v>
       </c>
       <c r="F120" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G120" s="30" t="n">
         <v>2</v>
@@ -36751,13 +36754,13 @@
     </row>
     <row r="121" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D121" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E121" s="28" t="n">
         <v>84</v>
       </c>
       <c r="F121" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G121" s="30" t="n">
         <v>2</v>
@@ -36826,13 +36829,13 @@
     </row>
     <row r="122" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D122" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E122" s="28" t="n">
         <v>87</v>
       </c>
       <c r="F122" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G122" s="30" t="n">
         <v>2</v>
@@ -36901,13 +36904,13 @@
     </row>
     <row r="123" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D123" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E123" s="28" t="n">
         <v>18</v>
       </c>
       <c r="F123" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G123" s="30" t="n">
         <v>3</v>
@@ -36976,13 +36979,13 @@
     </row>
     <row r="124" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D124" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E124" s="28" t="n">
         <v>31</v>
       </c>
       <c r="F124" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G124" s="30" t="n">
         <v>3</v>
@@ -37051,13 +37054,13 @@
     </row>
     <row r="125" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D125" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E125" s="28" t="n">
         <v>43</v>
       </c>
       <c r="F125" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G125" s="30" t="n">
         <v>3</v>
@@ -37126,13 +37129,13 @@
     </row>
     <row r="126" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D126" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E126" s="28" t="n">
         <v>48</v>
       </c>
       <c r="F126" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G126" s="30" t="n">
         <v>3</v>
@@ -37201,13 +37204,13 @@
     </row>
     <row r="127" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D127" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E127" s="28" t="n">
         <v>59</v>
       </c>
       <c r="F127" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G127" s="30" t="n">
         <v>3</v>
@@ -37276,13 +37279,13 @@
     </row>
     <row r="128" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D128" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E128" s="28" t="n">
         <v>60</v>
       </c>
       <c r="F128" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G128" s="30" t="n">
         <v>3</v>
@@ -37351,13 +37354,13 @@
     </row>
     <row r="129" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D129" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E129" s="28" t="n">
         <v>64</v>
       </c>
       <c r="F129" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G129" s="30" t="n">
         <v>3</v>
@@ -37426,13 +37429,13 @@
     </row>
     <row r="130" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E130" s="28" t="n">
         <v>80</v>
       </c>
       <c r="F130" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G130" s="30" t="n">
         <v>3</v>
@@ -37501,13 +37504,13 @@
     </row>
     <row r="131" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E131" s="28" t="n">
         <v>92</v>
       </c>
       <c r="F131" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G131" s="30" t="n">
         <v>3</v>
@@ -37576,13 +37579,13 @@
     </row>
     <row r="132" customFormat="false" ht="11.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D132" s="28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E132" s="28" t="n">
         <v>95</v>
       </c>
       <c r="F132" s="29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G132" s="30" t="n">
         <v>3</v>
